--- a/data/model_data/twfe_TER_pertrab.xlsx
+++ b/data/model_data/twfe_TER_pertrab.xlsx
@@ -388,16 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.1354889938630096</v>
+        <v>-0.3265580295809951</v>
       </c>
       <c r="C2">
-        <v>0.1714957389929141</v>
+        <v>2.426695324390646</v>
       </c>
       <c r="D2">
-        <v>-0.7900429168599213</v>
+        <v>-0.1345690273924252</v>
       </c>
       <c r="E2">
-        <v>0.4296022887231942</v>
+        <v>0.8929670282768535</v>
       </c>
     </row>
     <row r="3">
@@ -407,16 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.03315057209807776</v>
+        <v>-1.143610989099715</v>
       </c>
       <c r="C3">
-        <v>0.04619402368134311</v>
+        <v>0.6536536822465181</v>
       </c>
       <c r="D3">
-        <v>-0.7176376824577559</v>
+        <v>-1.749567118124816</v>
       </c>
       <c r="E3">
-        <v>0.4730698282614133</v>
+        <v>0.0803561077044775</v>
       </c>
     </row>
     <row r="4">
@@ -426,16 +426,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.3210279031436279</v>
+        <v>0.3014811259192695</v>
       </c>
       <c r="C4">
-        <v>0.2384177602591392</v>
+        <v>3.373653873093887</v>
       </c>
       <c r="D4">
-        <v>1.346493242763034</v>
+        <v>0.08936338381470926</v>
       </c>
       <c r="E4">
-        <v>0.1783057223505737</v>
+        <v>0.9288026360321813</v>
       </c>
     </row>
     <row r="5">
@@ -445,16 +445,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.4829891792748003</v>
+        <v>0.5224710773949297</v>
       </c>
       <c r="C5">
-        <v>0.2384177602591342</v>
+        <v>3.373653873093816</v>
       </c>
       <c r="D5">
-        <v>2.025810404182321</v>
+        <v>0.1548680146359521</v>
       </c>
       <c r="E5">
-        <v>0.04292513476347959</v>
+        <v>0.8769419853183931</v>
       </c>
     </row>
     <row r="6">
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.480675371142705</v>
+        <v>0.5524878730442448</v>
       </c>
       <c r="C6">
-        <v>0.2384177602590902</v>
+        <v>3.373653873093194</v>
       </c>
       <c r="D6">
-        <v>2.016105556147964</v>
+        <v>0.1637654287686859</v>
       </c>
       <c r="E6">
-        <v>0.04393085825640922</v>
+        <v>0.8699334016195038</v>
       </c>
     </row>
     <row r="7">
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.6471561324045657</v>
+        <v>0.6654965640669531</v>
       </c>
       <c r="C7">
-        <v>0.2392450476369511</v>
+        <v>3.385360137187985</v>
       </c>
       <c r="D7">
-        <v>2.70499280464359</v>
+        <v>0.1965807291095892</v>
       </c>
       <c r="E7">
-        <v>0.006892195094659403</v>
+        <v>0.8441768885345728</v>
       </c>
     </row>
     <row r="8">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2876524762334331</v>
+        <v>-0.07875048882514213</v>
       </c>
       <c r="C8">
-        <v>0.2392450476369432</v>
+        <v>3.385360137187873</v>
       </c>
       <c r="D8">
-        <v>1.202334088310779</v>
+        <v>-0.02326207128159724</v>
       </c>
       <c r="E8">
-        <v>0.2293854469962839</v>
+        <v>0.9814436935888924</v>
       </c>
     </row>
     <row r="9">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.008487501616329496</v>
+        <v>-0.1274961472586675</v>
       </c>
       <c r="C9">
-        <v>0.238417760259107</v>
+        <v>3.373653873093432</v>
       </c>
       <c r="D9">
-        <v>-0.03559928424420006</v>
+        <v>-0.03779170953947371</v>
       </c>
       <c r="E9">
-        <v>0.9716056563257149</v>
+        <v>0.9698577647046922</v>
       </c>
     </row>
     <row r="10">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.542092657446341</v>
+        <v>3.748579749458864</v>
       </c>
       <c r="C10">
-        <v>0.2392450476369575</v>
+        <v>3.385360137188075</v>
       </c>
       <c r="D10">
-        <v>6.445661770965435</v>
+        <v>1.107291277013879</v>
       </c>
       <c r="E10">
-        <v>1.458647410446055E-10</v>
+        <v>0.2683095915061093</v>
       </c>
     </row>
     <row r="11">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.240698902122355</v>
+        <v>2.160096624945445</v>
       </c>
       <c r="C11">
-        <v>0.2392450476369324</v>
+        <v>3.38536013718772</v>
       </c>
       <c r="D11">
-        <v>5.185891680421258</v>
+        <v>0.6380699652060876</v>
       </c>
       <c r="E11">
-        <v>2.381209575965227E-07</v>
+        <v>0.5235058055254243</v>
       </c>
     </row>
     <row r="12">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.7148466637814364</v>
+        <v>1.890856127115496</v>
       </c>
       <c r="C12">
-        <v>0.2392450476369555</v>
+        <v>3.385360137188047</v>
       </c>
       <c r="D12">
-        <v>2.987926692075928</v>
+        <v>0.5585391363076903</v>
       </c>
       <c r="E12">
-        <v>0.002845124013436561</v>
+        <v>0.5765427672665482</v>
       </c>
     </row>
     <row r="13">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9159500115724714</v>
+        <v>1.281496900879137</v>
       </c>
       <c r="C13">
-        <v>0.2392450476369156</v>
+        <v>3.385360137187483</v>
       </c>
       <c r="D13">
-        <v>3.828501449118982</v>
+        <v>0.3785407900335796</v>
       </c>
       <c r="E13">
-        <v>0.000133145221040376</v>
+        <v>0.7050716162613166</v>
       </c>
     </row>
     <row r="14">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.6923858394653434</v>
+        <v>1.120318084270635</v>
       </c>
       <c r="C14">
-        <v>0.2383625056774838</v>
+        <v>3.3728720108987</v>
       </c>
       <c r="D14">
-        <v>2.904759863542361</v>
+        <v>0.3321555281820869</v>
       </c>
       <c r="E14">
-        <v>0.003718257497044114</v>
+        <v>0.73980883045377</v>
       </c>
     </row>
     <row r="15">
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.8476811484540316</v>
+        <v>3.101025764494203</v>
       </c>
       <c r="C15">
-        <v>0.2392450476369518</v>
+        <v>3.385360137187995</v>
       </c>
       <c r="D15">
-        <v>3.543150242091389</v>
+        <v>0.9160105982313685</v>
       </c>
       <c r="E15">
-        <v>0.0004050217593413401</v>
+        <v>0.3597787540951423</v>
       </c>
     </row>
     <row r="16">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.7925609722478006</v>
+        <v>1.395828573958422</v>
       </c>
       <c r="C16">
-        <v>0.2383625056774747</v>
+        <v>3.372872010898571</v>
       </c>
       <c r="D16">
-        <v>3.325023665090201</v>
+        <v>0.4138397690301205</v>
       </c>
       <c r="E16">
-        <v>0.0009011024986503845</v>
+        <v>0.6790386364702521</v>
       </c>
     </row>
     <row r="17">
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.8284257872977657</v>
+        <v>1.307935867710672</v>
       </c>
       <c r="C17">
-        <v>0.2383625056774963</v>
+        <v>3.372872010898877</v>
       </c>
       <c r="D17">
-        <v>3.475486989630085</v>
+        <v>0.3877810552799792</v>
       </c>
       <c r="E17">
-        <v>0.0005214943176011403</v>
+        <v>0.6982219427423451</v>
       </c>
     </row>
     <row r="18">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.07439944109864018</v>
+        <v>-0.2764039750454176</v>
       </c>
       <c r="C18">
-        <v>0.23924504763692</v>
+        <v>3.385360137187544</v>
       </c>
       <c r="D18">
-        <v>0.3109758878334205</v>
+        <v>-0.08164684519356506</v>
       </c>
       <c r="E18">
-        <v>0.7558534091841231</v>
+        <v>0.9349362349382324</v>
       </c>
     </row>
     <row r="19">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.5404547436972938</v>
+        <v>0.8397153013628135</v>
       </c>
       <c r="C19">
-        <v>0.238362505677495</v>
+        <v>3.372872010898858</v>
       </c>
       <c r="D19">
-        <v>2.267364752527523</v>
+        <v>0.2489615077742106</v>
       </c>
       <c r="E19">
-        <v>0.02348098691263101</v>
+        <v>0.8034177365232614</v>
       </c>
     </row>
     <row r="20">
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.033369174985352</v>
+        <v>1.798683155630741</v>
       </c>
       <c r="C20">
-        <v>0.2383625056774966</v>
+        <v>3.372872010898881</v>
       </c>
       <c r="D20">
-        <v>4.335284075187126</v>
+        <v>0.5332793980378123</v>
       </c>
       <c r="E20">
-        <v>1.532679285259001E-05</v>
+        <v>0.5939031883360585</v>
       </c>
     </row>
     <row r="21">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.220249601922716</v>
+        <v>1.958942961211751</v>
       </c>
       <c r="C21">
-        <v>0.23924504763695</v>
+        <v>3.38536013718797</v>
       </c>
       <c r="D21">
-        <v>5.100417392022351</v>
+        <v>0.5786512754412404</v>
       </c>
       <c r="E21">
-        <v>3.730119956383351E-07</v>
+        <v>0.562893776084008</v>
       </c>
     </row>
     <row r="22">
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.6334988752352966</v>
+        <v>1.334332236411941</v>
       </c>
       <c r="C22">
-        <v>0.2383625056775121</v>
+        <v>3.3728720108991</v>
       </c>
       <c r="D22">
-        <v>2.657711930971125</v>
+        <v>0.3956071360253753</v>
       </c>
       <c r="E22">
-        <v>0.007933916541148344</v>
+        <v>0.692439734636717</v>
       </c>
     </row>
     <row r="23">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.150470830209473</v>
+        <v>1.736287089572682</v>
       </c>
       <c r="C23">
-        <v>0.2392450476369472</v>
+        <v>3.385360137187928</v>
       </c>
       <c r="D23">
-        <v>4.808755046647006</v>
+        <v>0.5128810582069829</v>
       </c>
       <c r="E23">
-        <v>1.639479325267202E-06</v>
+        <v>0.6080947483929633</v>
       </c>
     </row>
     <row r="24">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.1444122860879979</v>
+        <v>0.5822095400841929</v>
       </c>
       <c r="C24">
-        <v>0.239245047636953</v>
+        <v>3.385360137188012</v>
       </c>
       <c r="D24">
-        <v>0.6036166161614307</v>
+        <v>0.1719786127592897</v>
       </c>
       <c r="E24">
-        <v>0.5461713445863802</v>
+        <v>0.8634728430468728</v>
       </c>
     </row>
     <row r="25">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.007505021167950793</v>
+        <v>-0.302531434711571</v>
       </c>
       <c r="C25">
-        <v>0.2392450476369439</v>
+        <v>3.385360137187882</v>
       </c>
       <c r="D25">
-        <v>0.03136959883633503</v>
+        <v>-0.08936462368901017</v>
       </c>
       <c r="E25">
-        <v>0.974978113839559</v>
+        <v>0.9288016508309209</v>
       </c>
     </row>
     <row r="26">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.699416072799978</v>
+        <v>4.161405056892323</v>
       </c>
       <c r="C26">
-        <v>0.2392450476369311</v>
+        <v>3.385360137187702</v>
       </c>
       <c r="D26">
-        <v>7.103244516805821</v>
+        <v>1.229235557889359</v>
       </c>
       <c r="E26">
-        <v>1.721616322066539E-12</v>
+        <v>0.2191372456193326</v>
       </c>
     </row>
     <row r="27">
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.5526837402819093</v>
+        <v>-0.4532120218484672</v>
       </c>
       <c r="C27">
-        <v>0.2383625056774872</v>
+        <v>3.372872010898747</v>
       </c>
       <c r="D27">
-        <v>-2.318668948000193</v>
+        <v>-0.1343697657023466</v>
       </c>
       <c r="E27">
-        <v>0.02051970552423102</v>
+        <v>0.8931245634810109</v>
       </c>
     </row>
     <row r="28">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.1131446885653355</v>
+        <v>0.01038455247746126</v>
       </c>
       <c r="C28">
-        <v>0.2383625056774862</v>
+        <v>3.372872010898733</v>
       </c>
       <c r="D28">
-        <v>-0.4746748581273294</v>
+        <v>0.003078845697051576</v>
       </c>
       <c r="E28">
-        <v>0.6350738436782911</v>
+        <v>0.9975437669111409</v>
       </c>
     </row>
     <row r="29">
@@ -901,16 +901,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.6578516801567905</v>
+        <v>0.3986725003564705</v>
       </c>
       <c r="C29">
-        <v>0.2392450476369226</v>
+        <v>3.385360137187581</v>
       </c>
       <c r="D29">
-        <v>2.749698213837821</v>
+        <v>0.117763689593058</v>
       </c>
       <c r="E29">
-        <v>0.006022091185821895</v>
+        <v>0.9062674739377465</v>
       </c>
     </row>
     <row r="30">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.2745678398519558</v>
+        <v>-0.279794269955163</v>
       </c>
       <c r="C30">
-        <v>0.2383625056774621</v>
+        <v>3.372872010898393</v>
       </c>
       <c r="D30">
-        <v>-1.151891901251804</v>
+        <v>-0.08295430987333476</v>
       </c>
       <c r="E30">
-        <v>0.2495118786010576</v>
+        <v>0.9338966962095215</v>
       </c>
     </row>
     <row r="31">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.248573520308632</v>
+        <v>2.397118306906133</v>
       </c>
       <c r="C31">
-        <v>0.2392450476369299</v>
+        <v>3.385360137187685</v>
       </c>
       <c r="D31">
-        <v>5.218806126358881</v>
+        <v>0.7080836926547754</v>
       </c>
       <c r="E31">
-        <v>1.999638505944368E-07</v>
+        <v>0.4789810160612182</v>
       </c>
     </row>
     <row r="32">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.7400996761367703</v>
+        <v>-0.1517474910046957</v>
       </c>
       <c r="C32">
-        <v>0.2384177602590891</v>
+        <v>3.373653873093178</v>
       </c>
       <c r="D32">
-        <v>-3.104213693361193</v>
+        <v>-0.04498016000247353</v>
       </c>
       <c r="E32">
-        <v>0.001936270295738799</v>
+        <v>0.96412789740365</v>
       </c>
     </row>
     <row r="33">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.602953363459224</v>
+        <v>0.7280324452817259</v>
       </c>
       <c r="C33">
-        <v>0.238417760259132</v>
+        <v>3.373653873093784</v>
       </c>
       <c r="D33">
-        <v>2.52897838988121</v>
+        <v>0.2157993892284181</v>
       </c>
       <c r="E33">
-        <v>0.01152064123546227</v>
+        <v>0.8291675218068878</v>
       </c>
     </row>
     <row r="34">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.125157528563058</v>
+        <v>1.812701205085542</v>
       </c>
       <c r="C34">
-        <v>0.2392450476369239</v>
+        <v>3.3853601371876</v>
       </c>
       <c r="D34">
-        <v>4.702950132830279</v>
+        <v>0.535452989232469</v>
       </c>
       <c r="E34">
-        <v>2.750939253459796E-06</v>
+        <v>0.5923999560442561</v>
       </c>
     </row>
     <row r="35">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.7514266484449975</v>
+        <v>0.837988994780174</v>
       </c>
       <c r="C35">
-        <v>0.2392450476369342</v>
+        <v>3.385360137187746</v>
       </c>
       <c r="D35">
-        <v>3.140824254742039</v>
+        <v>0.2475331902136415</v>
       </c>
       <c r="E35">
-        <v>0.001710933499590748</v>
+        <v>0.8045226241456312</v>
       </c>
     </row>
     <row r="36">
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.625292751114134</v>
+        <v>4.524575765599915</v>
       </c>
       <c r="C36">
-        <v>0.2392450476369252</v>
+        <v>3.385360137187619</v>
       </c>
       <c r="D36">
-        <v>6.79342275699121</v>
+        <v>1.336512389301865</v>
       </c>
       <c r="E36">
-        <v>1.464226631354523E-11</v>
+        <v>0.1815434922544773</v>
       </c>
     </row>
     <row r="37">
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.0246835170009291</v>
+        <v>-0.5186142453802012</v>
       </c>
       <c r="C37">
-        <v>0.239245047636926</v>
+        <v>3.38536013718763</v>
       </c>
       <c r="D37">
-        <v>0.1031725306113268</v>
+        <v>-0.1531932274156915</v>
       </c>
       <c r="E37">
-        <v>0.9178370389311552</v>
+        <v>0.8782623299695156</v>
       </c>
     </row>
     <row r="38">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.1933388701736778</v>
+        <v>0.1385650469395743</v>
       </c>
       <c r="C38">
-        <v>0.2384177602590983</v>
+        <v>3.373653873093308</v>
       </c>
       <c r="D38">
-        <v>0.8109247816251965</v>
+        <v>0.04107269214684546</v>
       </c>
       <c r="E38">
-        <v>0.417511458208584</v>
+        <v>0.9672423036801792</v>
       </c>
     </row>
     <row r="39">
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.296520281520489</v>
+        <v>4.669155638474956</v>
       </c>
       <c r="C39">
-        <v>0.2392450476369448</v>
+        <v>3.385360137187896</v>
       </c>
       <c r="D39">
-        <v>5.419214710299721</v>
+        <v>1.379219772568559</v>
       </c>
       <c r="E39">
-        <v>6.756728524338062E-08</v>
+        <v>0.1679909622177373</v>
       </c>
     </row>
     <row r="40">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.1478443959769046</v>
+        <v>0.1419300698574363</v>
       </c>
       <c r="C40">
-        <v>0.238362505677507</v>
+        <v>3.372872010899028</v>
       </c>
       <c r="D40">
-        <v>0.6202502174437238</v>
+        <v>0.04207988604335012</v>
       </c>
       <c r="E40">
-        <v>0.5351681988559558</v>
+        <v>0.9664394805993112</v>
       </c>
     </row>
     <row r="41">
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.6008270063679676</v>
+        <v>0.8223570095626177</v>
       </c>
       <c r="C41">
-        <v>0.2383625056774989</v>
+        <v>3.372872010898913</v>
       </c>
       <c r="D41">
-        <v>2.520643943812531</v>
+        <v>0.2438150652931088</v>
       </c>
       <c r="E41">
-        <v>0.01179614600760344</v>
+        <v>0.8074006403469055</v>
       </c>
     </row>
     <row r="42">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.07859674932979392</v>
+        <v>0.4035313193171903</v>
       </c>
       <c r="C42">
-        <v>0.238362505677464</v>
+        <v>3.372872010898419</v>
       </c>
       <c r="D42">
-        <v>0.3297362104262561</v>
+        <v>0.1196402703729345</v>
       </c>
       <c r="E42">
-        <v>0.7416360053488249</v>
+        <v>0.9047808939337189</v>
       </c>
     </row>
     <row r="43">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.3908847697122123</v>
+        <v>0.5059087192134493</v>
       </c>
       <c r="C43">
-        <v>0.2383625056774894</v>
+        <v>3.372872010898778</v>
       </c>
       <c r="D43">
-        <v>1.639875233737849</v>
+        <v>0.1499934529323093</v>
       </c>
       <c r="E43">
-        <v>0.1011983204251308</v>
+        <v>0.8807858615643069</v>
       </c>
     </row>
     <row r="44">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.17252772250712</v>
+        <v>2.314388352613385</v>
       </c>
       <c r="C44">
-        <v>0.2383625056774743</v>
+        <v>3.372872010898565</v>
       </c>
       <c r="D44">
-        <v>4.919094633506055</v>
+        <v>0.6861773423761816</v>
       </c>
       <c r="E44">
-        <v>9.451243082051265E-07</v>
+        <v>0.4926858521893008</v>
       </c>
     </row>
     <row r="45">
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="B45">
-        <v>1.19593069221987</v>
+        <v>2.293003319490495</v>
       </c>
       <c r="C45">
-        <v>0.2383625056774995</v>
+        <v>3.372872010898922</v>
       </c>
       <c r="D45">
-        <v>5.017276894370056</v>
+        <v>0.6798370386071585</v>
       </c>
       <c r="E45">
-        <v>5.734597585897987E-07</v>
+        <v>0.4966913066487735</v>
       </c>
     </row>
     <row r="46">
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.4485568095795044</v>
+        <v>1.150862258676198</v>
       </c>
       <c r="C46">
-        <v>0.2383625056774618</v>
+        <v>3.372872010898388</v>
       </c>
       <c r="D46">
-        <v>1.881826205445521</v>
+        <v>0.3412113637747132</v>
       </c>
       <c r="E46">
-        <v>0.06001390140255019</v>
+        <v>0.7329825783608954</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.446668010130103</v>
+        <v>3.226039388266832</v>
       </c>
       <c r="C47">
-        <v>0.2384177602591271</v>
+        <v>3.373653873093716</v>
       </c>
       <c r="D47">
-        <v>6.067786261215505</v>
+        <v>0.9562449230479242</v>
       </c>
       <c r="E47">
-        <v>1.564197353667865E-09</v>
+        <v>0.3390713877377174</v>
       </c>
     </row>
     <row r="48">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.9368043166897</v>
+        <v>6.924414161697367</v>
       </c>
       <c r="C48">
-        <v>0.2383625056775176</v>
+        <v>3.372872010899178</v>
       </c>
       <c r="D48">
-        <v>8.125457110733752</v>
+        <v>2.052972700808585</v>
       </c>
       <c r="E48">
-        <v>7.986101677731847E-16</v>
+        <v>0.04021327443343529</v>
       </c>
     </row>
     <row r="49">
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.327571916752722</v>
+        <v>-0.1477690240737775</v>
       </c>
       <c r="C49">
-        <v>0.2392450476369453</v>
+        <v>3.385360137187903</v>
       </c>
       <c r="D49">
-        <v>1.369189958112791</v>
+        <v>-0.04364942519720337</v>
       </c>
       <c r="E49">
-        <v>0.1711033617962348</v>
+        <v>0.965188486514367</v>
       </c>
     </row>
     <row r="50">
@@ -1300,16 +1300,16 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.324338236060618</v>
+        <v>2.736537412775035</v>
       </c>
       <c r="C50">
-        <v>0.2383625056774895</v>
+        <v>3.37287201089878</v>
       </c>
       <c r="D50">
-        <v>5.55598386707883</v>
+        <v>0.8113374607552397</v>
       </c>
       <c r="E50">
-        <v>3.154191627881043E-08</v>
+        <v>0.4172745525691951</v>
       </c>
     </row>
     <row r="51">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.7765984302951626</v>
+        <v>1.143307330232925</v>
       </c>
       <c r="C51">
-        <v>0.2383625056774765</v>
+        <v>3.372872010898596</v>
       </c>
       <c r="D51">
-        <v>3.258056161508732</v>
+        <v>0.3389714541609085</v>
       </c>
       <c r="E51">
-        <v>0.001141768282211892</v>
+        <v>0.7346690710141127</v>
       </c>
     </row>
     <row r="52">
@@ -1338,16 +1338,16 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.2962232350508705</v>
+        <v>-0.258471670340474</v>
       </c>
       <c r="C52">
-        <v>0.2383625056775023</v>
+        <v>3.372872010898961</v>
       </c>
       <c r="D52">
-        <v>-1.242742579034859</v>
+        <v>-0.07663251659276106</v>
       </c>
       <c r="E52">
-        <v>0.2141176016942945</v>
+        <v>0.938924040231672</v>
       </c>
     </row>
     <row r="53">
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="B53">
-        <v>1.098303441601091</v>
+        <v>2.065827661458421</v>
       </c>
       <c r="C53">
-        <v>0.2383625056774977</v>
+        <v>3.372872010898896</v>
       </c>
       <c r="D53">
-        <v>4.607702199133138</v>
+        <v>0.6124832649395024</v>
       </c>
       <c r="E53">
-        <v>4.344767675576498E-06</v>
+        <v>0.5402921009710622</v>
       </c>
     </row>
     <row r="54">
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.473507557737773</v>
+        <v>0.6484738734937042</v>
       </c>
       <c r="C54">
-        <v>0.2383625056774927</v>
+        <v>3.372872010898825</v>
       </c>
       <c r="D54">
-        <v>1.986501846806537</v>
+        <v>0.1922616308588877</v>
       </c>
       <c r="E54">
-        <v>0.04712252148961058</v>
+        <v>0.8475580253130813</v>
       </c>
     </row>
     <row r="55">
@@ -1395,16 +1395,16 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.7911718122007566</v>
+        <v>1.187884916821914</v>
       </c>
       <c r="C55">
-        <v>0.2383625056774839</v>
+        <v>3.372872010898702</v>
       </c>
       <c r="D55">
-        <v>3.319195734883114</v>
+        <v>0.352187961174786</v>
       </c>
       <c r="E55">
-        <v>0.0009200089074436283</v>
+        <v>0.724736757903702</v>
       </c>
     </row>
     <row r="56">
@@ -1414,16 +1414,16 @@
         </is>
       </c>
       <c r="B56">
-        <v>1.497719237652684</v>
+        <v>3.811576063273221</v>
       </c>
       <c r="C56">
-        <v>0.2383625056774775</v>
+        <v>3.37287201089861</v>
       </c>
       <c r="D56">
-        <v>6.283367568216504</v>
+        <v>1.130068396001107</v>
       </c>
       <c r="E56">
-        <v>4.106177917627786E-10</v>
+        <v>0.2585914839604233</v>
       </c>
     </row>
     <row r="57">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9080590874017324</v>
+        <v>1.872359768693481</v>
       </c>
       <c r="C57">
-        <v>0.238362505677471</v>
+        <v>3.372872010898518</v>
       </c>
       <c r="D57">
-        <v>3.809571831865326</v>
+        <v>0.5551232785126325</v>
       </c>
       <c r="E57">
-        <v>0.0001436781215366309</v>
+        <v>0.5788763480781782</v>
       </c>
     </row>
     <row r="58">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.4271692819484059</v>
+        <v>1.09434513765333</v>
       </c>
       <c r="C58">
-        <v>0.2383625056774761</v>
+        <v>3.37287201089859</v>
       </c>
       <c r="D58">
-        <v>1.792099309974534</v>
+        <v>0.3244549849852673</v>
       </c>
       <c r="E58">
-        <v>0.07327772637052529</v>
+        <v>0.7456296736417815</v>
       </c>
     </row>
     <row r="59">
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.5609353944443926</v>
+        <v>0.8092357464690705</v>
       </c>
       <c r="C59">
-        <v>0.2383625056775046</v>
+        <v>3.372872010898994</v>
       </c>
       <c r="D59">
-        <v>2.353287035853351</v>
+        <v>0.2399248307834188</v>
       </c>
       <c r="E59">
-        <v>0.01871069755151947</v>
+        <v>0.8104146730639559</v>
       </c>
     </row>
     <row r="60">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.8705721106543762</v>
+        <v>2.886719228835007</v>
       </c>
       <c r="C60">
-        <v>0.2383625056775027</v>
+        <v>3.372872010898966</v>
       </c>
       <c r="D60">
-        <v>3.652303067464118</v>
+        <v>0.8558638511947609</v>
       </c>
       <c r="E60">
-        <v>0.0002670090258117966</v>
+        <v>0.3921820998524516</v>
       </c>
     </row>
     <row r="61">
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="B61">
-        <v>1.279145962310588</v>
+        <v>2.753376344875975</v>
       </c>
       <c r="C61">
-        <v>0.2383625056774912</v>
+        <v>3.372872010898804</v>
       </c>
       <c r="D61">
-        <v>5.366389141928622</v>
+        <v>0.8163299217933426</v>
       </c>
       <c r="E61">
-        <v>9.026328890371224E-08</v>
+        <v>0.4144148317708259</v>
       </c>
     </row>
     <row r="62">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.5110285646011579</v>
+        <v>0.7637265841947988</v>
       </c>
       <c r="C62">
-        <v>0.2383625056774802</v>
+        <v>3.372872010898648</v>
       </c>
       <c r="D62">
-        <v>2.143913377436183</v>
+        <v>0.2264321271981251</v>
       </c>
       <c r="E62">
-        <v>0.03216768324574334</v>
+        <v>0.8208899454200356</v>
       </c>
     </row>
     <row r="63">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.2020797068079987</v>
+        <v>0.4632159134025366</v>
       </c>
       <c r="C63">
-        <v>0.2383625056774909</v>
+        <v>3.3728720108988</v>
       </c>
       <c r="D63">
-        <v>0.8477831118347799</v>
+        <v>0.1373357518179586</v>
       </c>
       <c r="E63">
-        <v>0.3966666306082643</v>
+        <v>0.890780110521239</v>
       </c>
     </row>
     <row r="64">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="B64">
-        <v>1.747642180858785</v>
+        <v>4.780478592020922</v>
       </c>
       <c r="C64">
-        <v>0.2383625056774833</v>
+        <v>3.372872010898692</v>
       </c>
       <c r="D64">
-        <v>7.331866964108168</v>
+        <v>1.417331750678312</v>
       </c>
       <c r="E64">
-        <v>3.355224887957515E-13</v>
+        <v>0.1565515693504705</v>
       </c>
     </row>
     <row r="65">
@@ -1585,16 +1585,16 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.8334560777232894</v>
+        <v>1.276588716059776</v>
       </c>
       <c r="C65">
-        <v>0.2383625056775061</v>
+        <v>3.372872010899015</v>
       </c>
       <c r="D65">
-        <v>3.496590520200851</v>
+        <v>0.3784871503972397</v>
       </c>
       <c r="E65">
-        <v>0.0004821808548437089</v>
+        <v>0.7051114491233353</v>
       </c>
     </row>
     <row r="66">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="B66">
-        <v>1.182892382790554</v>
+        <v>2.467451458071244</v>
       </c>
       <c r="C66">
-        <v>0.2383625056775114</v>
+        <v>3.37287201089909</v>
       </c>
       <c r="D66">
-        <v>4.962577396257652</v>
+        <v>0.7315579868129973</v>
       </c>
       <c r="E66">
-        <v>7.583503153949639E-07</v>
+        <v>0.4645295251173145</v>
       </c>
     </row>
     <row r="67">
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="B67">
-        <v>-0.01941831965857597</v>
+        <v>-0.0463490044528478</v>
       </c>
       <c r="C67">
-        <v>0.2383625056774885</v>
+        <v>3.372872010898766</v>
       </c>
       <c r="D67">
-        <v>-0.08146549560462132</v>
+        <v>-0.01374170271005843</v>
       </c>
       <c r="E67">
-        <v>0.9350804311379733</v>
+        <v>0.9890375099144381</v>
       </c>
     </row>
     <row r="68">
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="B68">
-        <v>0.7096616145157919</v>
+        <v>1.165016247118699</v>
       </c>
       <c r="C68">
-        <v>0.2383625056774782</v>
+        <v>3.37287201089862</v>
       </c>
       <c r="D68">
-        <v>2.977236761707883</v>
+        <v>0.3454077840351577</v>
       </c>
       <c r="E68">
-        <v>0.002945748862804675</v>
+        <v>0.7298264479593326</v>
       </c>
     </row>
     <row r="69">
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.922947521875093</v>
+        <v>1.101468459873944</v>
       </c>
       <c r="C69">
-        <v>0.2392450476369372</v>
+        <v>3.385360137187788</v>
       </c>
       <c r="D69">
-        <v>3.857749746509689</v>
+        <v>0.3253622702572883</v>
       </c>
       <c r="E69">
-        <v>0.0001182913524448243</v>
+        <v>0.7449430933032544</v>
       </c>
     </row>
     <row r="70">
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.4745118658268849</v>
+        <v>0.1627055110377815</v>
       </c>
       <c r="C70">
-        <v>0.2392450476369336</v>
+        <v>3.385360137187738</v>
       </c>
       <c r="D70">
-        <v>1.983371737529048</v>
+        <v>0.04806150732694073</v>
       </c>
       <c r="E70">
-        <v>0.04747112220755428</v>
+        <v>0.9616723256686543</v>
       </c>
     </row>
     <row r="71">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.03677743817673559</v>
+        <v>-0.005394795776266937</v>
       </c>
       <c r="C71">
-        <v>0.2383625056775027</v>
+        <v>3.372872010898967</v>
       </c>
       <c r="D71">
-        <v>0.154292043843902</v>
+        <v>-0.001599466495862993</v>
       </c>
       <c r="E71">
-        <v>0.8773960224164726</v>
+        <v>0.9987239805263572</v>
       </c>
     </row>
     <row r="72">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.3756825200972927</v>
+        <v>0.2740037016046099</v>
       </c>
       <c r="C72">
-        <v>0.2384177602591201</v>
+        <v>3.373653873093617</v>
       </c>
       <c r="D72">
-        <v>1.57573210858532</v>
+        <v>0.08121867622221432</v>
       </c>
       <c r="E72">
-        <v>0.1152557140993351</v>
+        <v>0.9352766876503512</v>
       </c>
     </row>
     <row r="73">
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.1083784006036432</v>
+        <v>-0.1609923567969603</v>
       </c>
       <c r="C73">
-        <v>0.2383625056774892</v>
+        <v>3.372872010898776</v>
       </c>
       <c r="D73">
-        <v>-0.4546788946340498</v>
+        <v>-0.04773153451324123</v>
       </c>
       <c r="E73">
-        <v>0.6493927331544411</v>
+        <v>0.9619352689518526</v>
       </c>
     </row>
     <row r="74">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="B74">
-        <v>2.898410842168972</v>
+        <v>19.27104554597635</v>
       </c>
       <c r="C74">
-        <v>0.2384177602591132</v>
+        <v>3.373653873093518</v>
       </c>
       <c r="D74">
-        <v>12.15685794136716</v>
+        <v>5.712217752885686</v>
       </c>
       <c r="E74">
-        <v>8.648354090585541E-33</v>
+        <v>1.293504224202469E-08</v>
       </c>
     </row>
     <row r="75">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B75">
-        <v>2.064911870967789</v>
+        <v>11.19345342141472</v>
       </c>
       <c r="C75">
-        <v>0.2384177602591099</v>
+        <v>3.373653873093472</v>
       </c>
       <c r="D75">
-        <v>8.660897865677729</v>
+        <v>3.317902144819286</v>
       </c>
       <c r="E75">
-        <v>9.888661503317602E-18</v>
+        <v>0.0009242550344431342</v>
       </c>
     </row>
     <row r="76">
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="B76">
-        <v>2.387381997663135</v>
+        <v>10.45675446247185</v>
       </c>
       <c r="C76">
-        <v>0.2384177602591164</v>
+        <v>3.373653873093565</v>
       </c>
       <c r="D76">
-        <v>10.01344025322815</v>
+        <v>3.099533875086967</v>
       </c>
       <c r="E76">
-        <v>4.962586258840015E-23</v>
+        <v>0.001966962196180041</v>
       </c>
     </row>
     <row r="77">
@@ -1813,16 +1813,16 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.187193793542163</v>
+        <v>2.230226858056842</v>
       </c>
       <c r="C77">
-        <v>0.2384177602590935</v>
+        <v>3.37365387309324</v>
       </c>
       <c r="D77">
-        <v>4.979468778886332</v>
+        <v>0.661071627959269</v>
       </c>
       <c r="E77">
-        <v>6.958570663335114E-07</v>
+        <v>0.5086473378828151</v>
       </c>
     </row>
     <row r="78">
@@ -1832,16 +1832,16 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.674895455885028</v>
+        <v>4.253610574458086</v>
       </c>
       <c r="C78">
-        <v>0.2384177602590969</v>
+        <v>3.373653873093288</v>
       </c>
       <c r="D78">
-        <v>7.025044837535845</v>
+        <v>1.260831944967125</v>
       </c>
       <c r="E78">
-        <v>2.979572919568384E-12</v>
+        <v>0.2075257660142517</v>
       </c>
     </row>
     <row r="79">
@@ -1851,16 +1851,16 @@
         </is>
       </c>
       <c r="B79">
-        <v>1.568085712883853</v>
+        <v>3.897708282302772</v>
       </c>
       <c r="C79">
-        <v>0.2384177602591131</v>
+        <v>3.373653873093518</v>
       </c>
       <c r="D79">
-        <v>6.577050766602508</v>
+        <v>1.155337337178789</v>
       </c>
       <c r="E79">
-        <v>6.200036087151639E-11</v>
+        <v>0.2480990487967402</v>
       </c>
     </row>
     <row r="80">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B80">
-        <v>1.58696281820993</v>
+        <v>3.93080850335535</v>
       </c>
       <c r="C80">
-        <v>0.2384177602591217</v>
+        <v>3.373653873093639</v>
       </c>
       <c r="D80">
-        <v>6.65622735690981</v>
+        <v>1.165148723378312</v>
       </c>
       <c r="E80">
-        <v>3.674388899199595E-11</v>
+        <v>0.244106532083173</v>
       </c>
     </row>
     <row r="81">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B81">
-        <v>1.383657937204844</v>
+        <v>2.976139227657054</v>
       </c>
       <c r="C81">
-        <v>0.23841776025912</v>
+        <v>3.373653873093616</v>
       </c>
       <c r="D81">
-        <v>5.803501952627355</v>
+        <v>0.8821708864068962</v>
       </c>
       <c r="E81">
-        <v>7.604191542894041E-09</v>
+        <v>0.3777971200845279</v>
       </c>
     </row>
     <row r="82">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.8823422361323602</v>
+        <v>1.387561241174514</v>
       </c>
       <c r="C82">
-        <v>0.2384177602591217</v>
+        <v>3.373653873093639</v>
       </c>
       <c r="D82">
-        <v>3.700824280764135</v>
+        <v>0.4112933019717642</v>
       </c>
       <c r="E82">
-        <v>0.0002210811646308663</v>
+        <v>0.6809043349085924</v>
       </c>
     </row>
     <row r="83">
@@ -1927,16 +1927,16 @@
         </is>
       </c>
       <c r="B83">
-        <v>2.211059270854187</v>
+        <v>8.227210050664297</v>
       </c>
       <c r="C83">
-        <v>0.2383625056774825</v>
+        <v>3.372872010898681</v>
       </c>
       <c r="D83">
-        <v>9.27603636557618</v>
+        <v>2.439229838570781</v>
       </c>
       <c r="E83">
-        <v>4.673879867559714E-20</v>
+        <v>0.01481048180108984</v>
       </c>
     </row>
     <row r="84">
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="B84">
-        <v>3.850727578867188</v>
+        <v>127.5770869456695</v>
       </c>
       <c r="C84">
-        <v>0.2392450476369562</v>
+        <v>3.385360137188057</v>
       </c>
       <c r="D84">
-        <v>16.09532827074647</v>
+        <v>37.68493802010602</v>
       </c>
       <c r="E84">
-        <v>1.043942601198474E-54</v>
+        <v>5.069571344888056E-232</v>
       </c>
     </row>
     <row r="85">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.587505697193857</v>
+        <v>3.536240555097277</v>
       </c>
       <c r="C85">
-        <v>0.2392450476369303</v>
+        <v>3.385360137187691</v>
       </c>
       <c r="D85">
-        <v>6.635479868335658</v>
+        <v>1.044568498415335</v>
       </c>
       <c r="E85">
-        <v>4.216607984916327E-11</v>
+        <v>0.296356664324288</v>
       </c>
     </row>
     <row r="86">
@@ -1984,16 +1984,16 @@
         </is>
       </c>
       <c r="B86">
-        <v>1.569973019641002</v>
+        <v>3.898515815711239</v>
       </c>
       <c r="C86">
-        <v>0.2383625056774947</v>
+        <v>3.372872010898854</v>
       </c>
       <c r="D86">
-        <v>6.586493186831911</v>
+        <v>1.155844574924236</v>
       </c>
       <c r="E86">
-        <v>5.826774514051946E-11</v>
+        <v>0.2478915257525398</v>
       </c>
     </row>
     <row r="87">
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.743078685377384</v>
+        <v>4.729666894223033</v>
       </c>
       <c r="C87">
-        <v>0.2392450476369274</v>
+        <v>3.38536013718765</v>
       </c>
       <c r="D87">
-        <v>7.285746152717184</v>
+        <v>1.39709416503975</v>
       </c>
       <c r="E87">
-        <v>4.684305522871117E-13</v>
+        <v>0.1625500402428769</v>
       </c>
     </row>
     <row r="88">
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="B88">
-        <v>1.390633247920493</v>
+        <v>3.94257186269943</v>
       </c>
       <c r="C88">
-        <v>0.239245047636955</v>
+        <v>3.38536013718804</v>
       </c>
       <c r="D88">
-        <v>5.812589483694245</v>
+        <v>1.164594519617113</v>
       </c>
       <c r="E88">
-        <v>7.209452010710273E-09</v>
+        <v>0.2443308421344098</v>
       </c>
     </row>
     <row r="89">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.97472270991414</v>
+        <v>5.997918783984278</v>
       </c>
       <c r="C89">
-        <v>0.2392450476369225</v>
+        <v>3.38536013718758</v>
       </c>
       <c r="D89">
-        <v>8.253975283580258</v>
+        <v>1.771722517228878</v>
       </c>
       <c r="E89">
-        <v>2.848233632591998E-16</v>
+        <v>0.07660250092139284</v>
       </c>
     </row>
     <row r="90">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B90">
-        <v>2.537704320134432</v>
+        <v>13.42476707824801</v>
       </c>
       <c r="C90">
-        <v>0.2392450476369309</v>
+        <v>3.385360137187699</v>
       </c>
       <c r="D90">
-        <v>10.60713417142726</v>
+        <v>3.965535876310132</v>
       </c>
       <c r="E90">
-        <v>1.433505800956656E-25</v>
+        <v>7.597334766448798E-05</v>
       </c>
     </row>
     <row r="91">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="B91">
-        <v>3.959117183994686</v>
+        <v>55.22313344379721</v>
       </c>
       <c r="C91">
-        <v>0.2392450476369392</v>
+        <v>3.385360137187817</v>
       </c>
       <c r="D91">
-        <v>16.5483767505305</v>
+        <v>16.31233641501743</v>
       </c>
       <c r="E91">
-        <v>1.567601553076475E-57</v>
+        <v>4.715669433105614E-56</v>
       </c>
     </row>
     <row r="92">
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="B92">
-        <v>2.380674434828455</v>
+        <v>9.73737709551591</v>
       </c>
       <c r="C92">
-        <v>0.2392450476369285</v>
+        <v>3.385360137187666</v>
       </c>
       <c r="D92">
-        <v>9.95077832683625</v>
+        <v>2.876319416818407</v>
       </c>
       <c r="E92">
-        <v>9.041263435288801E-23</v>
+        <v>0.004068741330798402</v>
       </c>
     </row>
     <row r="93">
@@ -2117,16 +2117,16 @@
         </is>
       </c>
       <c r="B93">
-        <v>2.489040474923563</v>
+        <v>11.03060953290025</v>
       </c>
       <c r="C93">
-        <v>0.2392450476369381</v>
+        <v>3.385360137187801</v>
       </c>
       <c r="D93">
-        <v>10.4037283091467</v>
+        <v>3.258326761673078</v>
       </c>
       <c r="E93">
-        <v>1.09847225638415E-24</v>
+        <v>0.001140686164046533</v>
       </c>
     </row>
     <row r="94">
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="B94">
-        <v>2.115933628914889</v>
+        <v>7.548353420369545</v>
       </c>
       <c r="C94">
-        <v>0.239245047636934</v>
+        <v>3.385360137187744</v>
       </c>
       <c r="D94">
-        <v>8.844210778088586</v>
+        <v>2.229704703334767</v>
       </c>
       <c r="E94">
-        <v>2.075318966947129E-18</v>
+        <v>0.02588468730239674</v>
       </c>
     </row>
     <row r="95">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.305764756135479</v>
+        <v>6.494067923320923</v>
       </c>
       <c r="C95">
-        <v>0.2672438713521639</v>
+        <v>3.781548491470958</v>
       </c>
       <c r="D95">
-        <v>4.886041911938896</v>
+        <v>1.717303887010277</v>
       </c>
       <c r="E95">
-        <v>1.115995386227455E-06</v>
+        <v>0.08608826605339577</v>
       </c>
     </row>
     <row r="96">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="B96">
-        <v>3.011580375050972</v>
+        <v>21.46729878900714</v>
       </c>
       <c r="C96">
-        <v>0.2463742888968899</v>
+        <v>3.486240173820621</v>
       </c>
       <c r="D96">
-        <v>12.22359844663559</v>
+        <v>6.157722279208554</v>
       </c>
       <c r="E96">
-        <v>4.048525526954751E-33</v>
+        <v>8.999613578536962E-10</v>
       </c>
     </row>
     <row r="97">
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="B97">
-        <v>2.254389677584449</v>
+        <v>9.348174506440728</v>
       </c>
       <c r="C97">
-        <v>0.2384177602590911</v>
+        <v>3.373653873093206</v>
       </c>
       <c r="D97">
-        <v>9.455628117362481</v>
+        <v>2.770934677382792</v>
       </c>
       <c r="E97">
-        <v>9.203574009789703E-21</v>
+        <v>0.005644551862827974</v>
       </c>
     </row>
     <row r="98">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="B98">
-        <v>2.022585667669073</v>
+        <v>6.279535918076763</v>
       </c>
       <c r="C98">
-        <v>0.2392450476369342</v>
+        <v>3.385360137187745</v>
       </c>
       <c r="D98">
-        <v>8.454033584588315</v>
+        <v>1.854909275115776</v>
       </c>
       <c r="E98">
-        <v>5.55858492648487E-17</v>
+        <v>0.06376555906661685</v>
       </c>
     </row>
     <row r="99">
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="B99">
-        <v>2.09945766110183</v>
+        <v>9.042834257962522</v>
       </c>
       <c r="C99">
-        <v>0.239245047636923</v>
+        <v>3.385360137187587</v>
       </c>
       <c r="D99">
-        <v>8.775344283355681</v>
+        <v>2.671158722118977</v>
       </c>
       <c r="E99">
-        <v>3.743757785616853E-18</v>
+        <v>0.007624153545474164</v>
       </c>
     </row>
     <row r="100">
@@ -2250,16 +2250,16 @@
         </is>
       </c>
       <c r="B100">
-        <v>2.943248931152397</v>
+        <v>21.39801746021478</v>
       </c>
       <c r="C100">
-        <v>0.2392450476369445</v>
+        <v>3.385360137187892</v>
       </c>
       <c r="D100">
-        <v>12.30223555397808</v>
+        <v>6.320750700984332</v>
       </c>
       <c r="E100">
-        <v>1.648003302603802E-33</v>
+        <v>3.242130826198829E-10</v>
       </c>
     </row>
     <row r="101">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="B101">
-        <v>1.20418263656386</v>
+        <v>2.454323882258456</v>
       </c>
       <c r="C101">
-        <v>0.2383625056774869</v>
+        <v>3.372872010898743</v>
       </c>
       <c r="D101">
-        <v>5.051896199619426</v>
+        <v>0.7276658806879753</v>
       </c>
       <c r="E101">
-        <v>4.798073616619708E-07</v>
+        <v>0.4669087036230977</v>
       </c>
     </row>
     <row r="102">
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="B102">
-        <v>2.658628846502293</v>
+        <v>16.99963345280252</v>
       </c>
       <c r="C102">
-        <v>0.2384177602591264</v>
+        <v>3.373653873093706</v>
       </c>
       <c r="D102">
-        <v>11.15113590368746</v>
+        <v>5.038938223147807</v>
       </c>
       <c r="E102">
-        <v>5.227324939755494E-28</v>
+        <v>5.129885713513646E-07</v>
       </c>
     </row>
     <row r="103">
@@ -2307,16 +2307,16 @@
         </is>
       </c>
       <c r="B103">
-        <v>1.276453588865215</v>
+        <v>3.315732193691889</v>
       </c>
       <c r="C103">
-        <v>0.2384177602591232</v>
+        <v>3.373653873093661</v>
       </c>
       <c r="D103">
-        <v>5.353852781260536</v>
+        <v>0.9828311730898885</v>
       </c>
       <c r="E103">
-        <v>9.664843639476231E-08</v>
+        <v>0.3258169323850176</v>
       </c>
     </row>
     <row r="104">
@@ -2326,16 +2326,16 @@
         </is>
       </c>
       <c r="B104">
-        <v>1.514138277795636</v>
+        <v>5.362577175139684</v>
       </c>
       <c r="C104">
-        <v>0.2384177602591223</v>
+        <v>3.373653873093648</v>
       </c>
       <c r="D104">
-        <v>6.350778046694204</v>
+        <v>1.589545749760686</v>
       </c>
       <c r="E104">
-        <v>2.679232580351824E-10</v>
+        <v>0.1121052838291688</v>
       </c>
     </row>
     <row r="105">
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.2774916884931372</v>
+        <v>0.3327233419770296</v>
       </c>
       <c r="C105">
-        <v>0.2384177602591128</v>
+        <v>3.373653873093513</v>
       </c>
       <c r="D105">
-        <v>1.163888496358488</v>
+        <v>0.0986240303519741</v>
       </c>
       <c r="E105">
-        <v>0.2446168097810968</v>
+        <v>0.9214472979750731</v>
       </c>
     </row>
     <row r="106">
@@ -2364,16 +2364,16 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.331252180330909</v>
+        <v>3.001101043540522</v>
       </c>
       <c r="C106">
-        <v>0.238417760259124</v>
+        <v>3.373653873093672</v>
       </c>
       <c r="D106">
-        <v>5.583695522028388</v>
+        <v>0.8895699311288517</v>
       </c>
       <c r="E106">
-        <v>2.697353013325152E-08</v>
+        <v>0.373810609811737</v>
       </c>
     </row>
     <row r="107">
@@ -2383,16 +2383,16 @@
         </is>
       </c>
       <c r="B107">
-        <v>1.45067651198236</v>
+        <v>3.967836981781101</v>
       </c>
       <c r="C107">
-        <v>0.2384177602591224</v>
+        <v>3.37365387309365</v>
       </c>
       <c r="D107">
-        <v>6.084599194312136</v>
+        <v>1.176124502109217</v>
       </c>
       <c r="E107">
-        <v>1.411424887442895E-09</v>
+        <v>0.2396939553464212</v>
       </c>
     </row>
     <row r="108">
@@ -2402,16 +2402,16 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.345060271786013</v>
+        <v>-0.05270835846933247</v>
       </c>
       <c r="C108">
-        <v>0.2392450476369363</v>
+        <v>3.385360137187775</v>
       </c>
       <c r="D108">
-        <v>1.442288043970947</v>
+        <v>-0.0155694981725393</v>
       </c>
       <c r="E108">
-        <v>0.1493876111323743</v>
+        <v>0.9875794908269762</v>
       </c>
     </row>
     <row r="109">
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.9448370551987437</v>
+        <v>1.556055512815207</v>
       </c>
       <c r="C109">
-        <v>0.2384177602591057</v>
+        <v>3.373653873093413</v>
       </c>
       <c r="D109">
-        <v>3.962947450609055</v>
+        <v>0.4612374509505947</v>
       </c>
       <c r="E109">
-        <v>7.679516367777968E-05</v>
+        <v>0.6446815829447634</v>
       </c>
     </row>
     <row r="110">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="B110">
-        <v>1.607627120012932</v>
+        <v>3.738270872757836</v>
       </c>
       <c r="C110">
-        <v>0.2392450476369308</v>
+        <v>3.385360137187698</v>
       </c>
       <c r="D110">
-        <v>6.719583689993894</v>
+        <v>1.104246142587155</v>
       </c>
       <c r="E110">
-        <v>2.407614882824385E-11</v>
+        <v>0.2696276138087106</v>
       </c>
     </row>
     <row r="111">
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.608256150951939</v>
+        <v>3.903465451546818</v>
       </c>
       <c r="C111">
-        <v>0.2384177602591216</v>
+        <v>3.373653873093639</v>
       </c>
       <c r="D111">
-        <v>6.745538374339329</v>
+        <v>1.157043845747976</v>
       </c>
       <c r="E111">
-        <v>2.022625074068199E-11</v>
+        <v>0.247401359124526</v>
       </c>
     </row>
     <row r="112">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="B112">
-        <v>1.58196852521414</v>
+        <v>4.950287031206083</v>
       </c>
       <c r="C112">
-        <v>0.2384177602591251</v>
+        <v>3.373653873093688</v>
       </c>
       <c r="D112">
-        <v>6.63527970187612</v>
+        <v>1.467336963844071</v>
       </c>
       <c r="E112">
-        <v>4.222203102839009E-11</v>
+        <v>0.1424515880474894</v>
       </c>
     </row>
     <row r="113">
@@ -2497,16 +2497,16 @@
         </is>
       </c>
       <c r="B113">
-        <v>1.189610582847264</v>
+        <v>2.405004403355369</v>
       </c>
       <c r="C113">
-        <v>0.2383625056774772</v>
+        <v>3.372872010898607</v>
       </c>
       <c r="D113">
-        <v>4.99076219838408</v>
+        <v>0.7130434821078858</v>
       </c>
       <c r="E113">
-        <v>6.568771626102354E-07</v>
+        <v>0.4759072980720989</v>
       </c>
     </row>
     <row r="114">
@@ -2516,16 +2516,16 @@
         </is>
       </c>
       <c r="B114">
-        <v>1.975250028701796</v>
+        <v>6.370899283355911</v>
       </c>
       <c r="C114">
-        <v>0.2383625056774974</v>
+        <v>3.372872010898892</v>
       </c>
       <c r="D114">
-        <v>8.286748048261808</v>
+        <v>1.888864819883286</v>
       </c>
       <c r="E114">
-        <v>2.184639932325001E-16</v>
+        <v>0.05906365915799015</v>
       </c>
     </row>
     <row r="115">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.9481883437913265</v>
+        <v>1.872044993791578</v>
       </c>
       <c r="C115">
-        <v>0.2384177602591195</v>
+        <v>3.373653873093608</v>
       </c>
       <c r="D115">
-        <v>3.977003822034094</v>
+        <v>0.5549013218937399</v>
       </c>
       <c r="E115">
-        <v>7.243141141863329E-05</v>
+        <v>0.5790281336933367</v>
       </c>
     </row>
     <row r="116">
@@ -2554,16 +2554,16 @@
         </is>
       </c>
       <c r="B116">
-        <v>1.147623945654751</v>
+        <v>2.292668619498772</v>
       </c>
       <c r="C116">
-        <v>0.2384177602591318</v>
+        <v>3.373653873093782</v>
       </c>
       <c r="D116">
-        <v>4.813500237597315</v>
+        <v>0.6795802728263582</v>
       </c>
       <c r="E116">
-        <v>1.601471989549606E-06</v>
+        <v>0.4968538823409641</v>
       </c>
     </row>
     <row r="117">
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.7242470004179803</v>
+        <v>0.7438150149088192</v>
       </c>
       <c r="C117">
-        <v>0.2392450476369297</v>
+        <v>3.385360137187682</v>
       </c>
       <c r="D117">
-        <v>3.02721835863066</v>
+        <v>0.2197151808867012</v>
       </c>
       <c r="E117">
-        <v>0.002501670471193688</v>
+        <v>0.8261168213327168</v>
       </c>
     </row>
     <row r="118">
@@ -2592,16 +2592,16 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.745732384008069</v>
+        <v>0.9304680137984688</v>
       </c>
       <c r="C118">
-        <v>0.2384177602591233</v>
+        <v>3.373653873093661</v>
       </c>
       <c r="D118">
-        <v>3.12783906365689</v>
+        <v>0.2758042314949233</v>
       </c>
       <c r="E118">
-        <v>0.001787937906766248</v>
+        <v>0.7827287293316503</v>
       </c>
     </row>
     <row r="119">
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.327099882852089</v>
+        <v>2.770248086098746</v>
       </c>
       <c r="C119">
-        <v>0.2383625056774864</v>
+        <v>3.372872010898736</v>
       </c>
       <c r="D119">
-        <v>5.567569778141645</v>
+        <v>0.8213321101859971</v>
       </c>
       <c r="E119">
-        <v>2.954720214619927E-08</v>
+        <v>0.4115612061991961</v>
       </c>
     </row>
     <row r="120">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.8426569785156481</v>
+        <v>1.274040172811422</v>
       </c>
       <c r="C120">
-        <v>0.238362505677483</v>
+        <v>3.372872010898688</v>
       </c>
       <c r="D120">
-        <v>3.535190973599712</v>
+        <v>0.3777315500542694</v>
       </c>
       <c r="E120">
-        <v>0.0004173362384467771</v>
+        <v>0.7056726448217081</v>
       </c>
     </row>
     <row r="121">
@@ -2649,16 +2649,16 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.6224314858209394</v>
+        <v>0.8489355276002012</v>
       </c>
       <c r="C121">
-        <v>0.2383625056774785</v>
+        <v>3.372872010898625</v>
       </c>
       <c r="D121">
-        <v>2.611281015241271</v>
+        <v>0.2516951502627642</v>
       </c>
       <c r="E121">
-        <v>0.009092074890644427</v>
+        <v>0.8013042010162477</v>
       </c>
     </row>
     <row r="122">
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="B122">
-        <v>0.6710603894827263</v>
+        <v>0.7843610998010982</v>
       </c>
       <c r="C122">
-        <v>0.2384177602591014</v>
+        <v>3.373653873093351</v>
       </c>
       <c r="D122">
-        <v>2.814640942660685</v>
+        <v>0.2324960204295962</v>
       </c>
       <c r="E122">
-        <v>0.004934013929834061</v>
+        <v>0.8161780708798956</v>
       </c>
     </row>
     <row r="123">
@@ -2687,16 +2687,16 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.6353191732532406</v>
+        <v>0.7725909759031686</v>
       </c>
       <c r="C123">
-        <v>0.2384177602591187</v>
+        <v>3.373653873093597</v>
       </c>
       <c r="D123">
-        <v>2.664730901602125</v>
+        <v>0.2290071847811443</v>
       </c>
       <c r="E123">
-        <v>0.007770846345101861</v>
+        <v>0.8188882273917421</v>
       </c>
     </row>
     <row r="124">
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.174096670078896</v>
+        <v>2.423902600567029</v>
       </c>
       <c r="C124">
-        <v>0.238417760259115</v>
+        <v>3.373653873093544</v>
       </c>
       <c r="D124">
-        <v>4.924535272887705</v>
+        <v>0.7184799305876568</v>
       </c>
       <c r="E124">
-        <v>9.195315162818017E-07</v>
+        <v>0.4725506514764288</v>
       </c>
     </row>
     <row r="125">
@@ -2725,16 +2725,16 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.5058692854562535</v>
+        <v>0.5286641600124802</v>
       </c>
       <c r="C125">
-        <v>0.2384177602591003</v>
+        <v>3.373653873093336</v>
       </c>
       <c r="D125">
-        <v>2.121776854654203</v>
+        <v>0.1567037342594197</v>
       </c>
       <c r="E125">
-        <v>0.03398689059429678</v>
+        <v>0.8754951607818932</v>
       </c>
     </row>
     <row r="126">
@@ -2744,16 +2744,16 @@
         </is>
       </c>
       <c r="B126">
-        <v>2.58538767931093</v>
+        <v>12.5999840748241</v>
       </c>
       <c r="C126">
-        <v>0.2392450476369432</v>
+        <v>3.385360137187873</v>
       </c>
       <c r="D126">
-        <v>10.80644178363216</v>
+        <v>3.721903597911024</v>
       </c>
       <c r="E126">
-        <v>1.885358767947938E-26</v>
+        <v>0.00020353752117615</v>
       </c>
     </row>
     <row r="127">
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="B127">
-        <v>1.258291404242172</v>
+        <v>2.49864119333263</v>
       </c>
       <c r="C127">
-        <v>0.2384177602591209</v>
+        <v>3.373653873093629</v>
       </c>
       <c r="D127">
-        <v>5.277674796016104</v>
+        <v>0.7406335348330754</v>
       </c>
       <c r="E127">
-        <v>1.459522615346362E-07</v>
+        <v>0.4590081085324044</v>
       </c>
     </row>
     <row r="128">
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.012034168160034</v>
+        <v>2.341997368736303</v>
       </c>
       <c r="C128">
-        <v>0.2384177602591202</v>
+        <v>3.373653873093618</v>
       </c>
       <c r="D128">
-        <v>4.244793538283903</v>
+        <v>0.6942020304497648</v>
       </c>
       <c r="E128">
-        <v>2.294501527183414E-05</v>
+        <v>0.4876412450531196</v>
       </c>
     </row>
     <row r="129">
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="B129">
-        <v>-0.06744614651828626</v>
+        <v>-0.2633353876958107</v>
       </c>
       <c r="C129">
-        <v>0.2384177602591098</v>
+        <v>3.373653873093471</v>
       </c>
       <c r="D129">
-        <v>-0.2828906137067412</v>
+        <v>-0.0780564330549848</v>
       </c>
       <c r="E129">
-        <v>0.777291816915981</v>
+        <v>0.9377914648559096</v>
       </c>
     </row>
     <row r="130">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="B130">
-        <v>-0.1389269177505527</v>
+        <v>0.1139448655981404</v>
       </c>
       <c r="C130">
-        <v>0.2384177602591095</v>
+        <v>3.373653873093466</v>
       </c>
       <c r="D130">
-        <v>-0.5827037281097208</v>
+        <v>0.03377491286432974</v>
       </c>
       <c r="E130">
-        <v>0.5601626066324421</v>
+        <v>0.9730602246350997</v>
       </c>
     </row>
     <row r="131">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.6499021384255256</v>
+        <v>0.8819206444780845</v>
       </c>
       <c r="C131">
-        <v>0.2383625056774876</v>
+        <v>3.372872010898753</v>
       </c>
       <c r="D131">
-        <v>2.7265283882561</v>
+        <v>0.2614746843723499</v>
       </c>
       <c r="E131">
-        <v>0.006459844670335133</v>
+        <v>0.7937550959090561</v>
       </c>
     </row>
     <row r="132">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B132">
-        <v>1.757360187411558</v>
+        <v>4.81035308628573</v>
       </c>
       <c r="C132">
-        <v>0.2384177602591124</v>
+        <v>3.373653873093508</v>
       </c>
       <c r="D132">
-        <v>7.37092817876344</v>
+        <v>1.425858510456743</v>
       </c>
       <c r="E132">
-        <v>2.525400123386536E-13</v>
+        <v>0.1540751160250563</v>
       </c>
     </row>
     <row r="133">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="B133">
-        <v>1.776838744726661</v>
+        <v>5.082234800154092</v>
       </c>
       <c r="C133">
-        <v>0.2383625056774814</v>
+        <v>3.372872010898665</v>
       </c>
       <c r="D133">
-        <v>7.454355036571187</v>
+        <v>1.506797406996771</v>
       </c>
       <c r="E133">
-        <v>1.370231678452504E-13</v>
+        <v>0.1320305086881897</v>
       </c>
     </row>
     <row r="134">
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="B134">
-        <v>1.70585010974713</v>
+        <v>4.786693090291432</v>
       </c>
       <c r="C134">
-        <v>0.2384177602591172</v>
+        <v>3.373653873093575</v>
       </c>
       <c r="D134">
-        <v>7.154878511958076</v>
+        <v>1.41884534405485</v>
       </c>
       <c r="E134">
-        <v>1.194889812482844E-12</v>
+        <v>0.1561097801129068</v>
       </c>
     </row>
     <row r="135">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="B135">
-        <v>2.566601661374282</v>
+        <v>12.20923906662509</v>
       </c>
       <c r="C135">
-        <v>0.2392450476369331</v>
+        <v>3.38536013718773</v>
       </c>
       <c r="D135">
-        <v>10.72791970711651</v>
+        <v>3.606481606641557</v>
       </c>
       <c r="E135">
-        <v>4.209081104668118E-26</v>
+        <v>0.0003184716541712537</v>
       </c>
     </row>
     <row r="136">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B136">
-        <v>3.686925133541449</v>
+        <v>51.97560043959331</v>
       </c>
       <c r="C136">
-        <v>0.2384177602591136</v>
+        <v>3.373653873093525</v>
       </c>
       <c r="D136">
-        <v>15.4641379464956</v>
+        <v>15.40632275709229</v>
       </c>
       <c r="E136">
-        <v>7.139136420372474E-51</v>
+        <v>1.581491178451645E-50</v>
       </c>
     </row>
     <row r="137">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B137">
-        <v>3.920017722400877</v>
+        <v>51.74969244339196</v>
       </c>
       <c r="C137">
-        <v>0.2384177602591109</v>
+        <v>3.373653873093487</v>
       </c>
       <c r="D137">
-        <v>16.44180248208282</v>
+        <v>15.33936034639495</v>
       </c>
       <c r="E137">
-        <v>7.322419989700512E-57</v>
+        <v>3.961836252931322E-50</v>
       </c>
     </row>
     <row r="138">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B138">
-        <v>2.539372919773875</v>
+        <v>13.72321936509242</v>
       </c>
       <c r="C138">
-        <v>0.2384177602590994</v>
+        <v>3.373653873093323</v>
       </c>
       <c r="D138">
-        <v>10.65093857527318</v>
+        <v>4.067761507646757</v>
       </c>
       <c r="E138">
-        <v>9.204312047188656E-26</v>
+        <v>4.942720195246581E-05</v>
       </c>
     </row>
     <row r="139">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B139">
-        <v>1.647154392664955</v>
+        <v>4.160733588103136</v>
       </c>
       <c r="C139">
-        <v>0.2384177602591208</v>
+        <v>3.373653873093626</v>
       </c>
       <c r="D139">
-        <v>6.908689985489211</v>
+        <v>1.23330185745693</v>
       </c>
       <c r="E139">
-        <v>6.670346124145335E-12</v>
+        <v>0.2176172603402981</v>
       </c>
     </row>
     <row r="140">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B140">
-        <v>2.776552235801073</v>
+        <v>16.38681305817074</v>
       </c>
       <c r="C140">
-        <v>0.2384177602591145</v>
+        <v>3.373653873093538</v>
       </c>
       <c r="D140">
-        <v>11.64574414583667</v>
+        <v>4.857289358835299</v>
       </c>
       <c r="E140">
-        <v>2.574752921830897E-30</v>
+        <v>1.288510280873369E-06</v>
       </c>
     </row>
     <row r="141">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.407490730490635</v>
+        <v>3.665924482323477</v>
       </c>
       <c r="C141">
-        <v>0.2384177602591089</v>
+        <v>3.373653873093458</v>
       </c>
       <c r="D141">
-        <v>5.903464276155414</v>
+        <v>1.086633252913412</v>
       </c>
       <c r="E141">
-        <v>4.212867451698524E-09</v>
+        <v>0.2773381497899959</v>
       </c>
     </row>
     <row r="142">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B142">
-        <v>2.436590677493996</v>
+        <v>10.59702201825448</v>
       </c>
       <c r="C142">
-        <v>0.239245047636935</v>
+        <v>3.385360137187758</v>
       </c>
       <c r="D142">
-        <v>10.1844978676074</v>
+        <v>3.130249541798381</v>
       </c>
       <c r="E142">
-        <v>9.488785697072023E-24</v>
+        <v>0.001773406677189616</v>
       </c>
     </row>
     <row r="143">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B143">
-        <v>3.638573301364333</v>
+        <v>41.17887246541327</v>
       </c>
       <c r="C143">
-        <v>0.239245047636931</v>
+        <v>3.3853601371877</v>
       </c>
       <c r="D143">
-        <v>15.20856267372393</v>
+        <v>12.16380851569356</v>
       </c>
       <c r="E143">
-        <v>2.360858187840382E-49</v>
+        <v>7.992355992390432E-33</v>
       </c>
     </row>
     <row r="144">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B144">
-        <v>2.253470703661315</v>
+        <v>8.630495447873821</v>
       </c>
       <c r="C144">
-        <v>0.2392450476369379</v>
+        <v>3.385360137187798</v>
       </c>
       <c r="D144">
-        <v>9.41909028387091</v>
+        <v>2.549358147474121</v>
       </c>
       <c r="E144">
-        <v>1.283836418825458E-20</v>
+        <v>0.01087089588087127</v>
       </c>
     </row>
     <row r="145">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B145">
-        <v>2.078554684776472</v>
+        <v>7.825285461714487</v>
       </c>
       <c r="C145">
-        <v>0.2392450476369286</v>
+        <v>3.385360137187666</v>
       </c>
       <c r="D145">
-        <v>8.687973712755079</v>
+        <v>2.311507533793795</v>
       </c>
       <c r="E145">
-        <v>7.86664562756981E-18</v>
+        <v>0.02091243419886754</v>
       </c>
     </row>
     <row r="146">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B146">
-        <v>1.654715771938132</v>
+        <v>4.251131328689556</v>
       </c>
       <c r="C146">
-        <v>0.2384177602591188</v>
+        <v>3.373653873093598</v>
       </c>
       <c r="D146">
-        <v>6.940404817744041</v>
+        <v>1.260097060517747</v>
       </c>
       <c r="E146">
-        <v>5.361411508825547E-12</v>
+        <v>0.207790656585106</v>
       </c>
     </row>
     <row r="147">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.44100583455714</v>
+        <v>2.786313170965068</v>
       </c>
       <c r="C147">
-        <v>0.2392450476369309</v>
+        <v>3.385360137187699</v>
       </c>
       <c r="D147">
-        <v>6.023137568740631</v>
+        <v>0.8230477875478637</v>
       </c>
       <c r="E147">
-        <v>2.052456471420613E-09</v>
+        <v>0.4105851483555684</v>
       </c>
     </row>
     <row r="148">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B148">
-        <v>2.185404277408731</v>
+        <v>7.913299256787216</v>
       </c>
       <c r="C148">
-        <v>0.2384177602591047</v>
+        <v>3.373653873093398</v>
       </c>
       <c r="D148">
-        <v>9.166281383709439</v>
+        <v>2.345616816206249</v>
       </c>
       <c r="E148">
-        <v>1.24461104371891E-19</v>
+        <v>0.01909900667719257</v>
       </c>
     </row>
     <row r="149">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.2310208204230013</v>
+        <v>0.1265408882036819</v>
       </c>
       <c r="C149">
-        <v>0.2384177602591045</v>
+        <v>3.373653873093397</v>
       </c>
       <c r="D149">
-        <v>0.9689748791026955</v>
+        <v>0.03750855688335718</v>
       </c>
       <c r="E149">
-        <v>0.3326822959298416</v>
+        <v>0.9700834976779178</v>
       </c>
     </row>
     <row r="150">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B150">
-        <v>2.035726221391056</v>
+        <v>6.911726488078882</v>
       </c>
       <c r="C150">
-        <v>0.2384177602591167</v>
+        <v>3.373653873093568</v>
       </c>
       <c r="D150">
-        <v>8.538483958487793</v>
+        <v>2.048736102776595</v>
       </c>
       <c r="E150">
-        <v>2.759460899757654E-17</v>
+        <v>0.04062642952562222</v>
       </c>
     </row>
     <row r="151">
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.60345471818732</v>
+        <v>4.117755200078614</v>
       </c>
       <c r="C151">
-        <v>0.2383625056775022</v>
+        <v>3.37287201089896</v>
       </c>
       <c r="D151">
-        <v>6.726958644900089</v>
+        <v>1.220845376513745</v>
       </c>
       <c r="E151">
-        <v>2.291459656971488E-11</v>
+        <v>0.222297579534996</v>
       </c>
     </row>
     <row r="152">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B152">
-        <v>3.64668709426131</v>
+        <v>38.43769056682537</v>
       </c>
       <c r="C152">
-        <v>0.2383625056774953</v>
+        <v>3.372872010898862</v>
       </c>
       <c r="D152">
-        <v>15.29891240191643</v>
+        <v>11.39613078783319</v>
       </c>
       <c r="E152">
-        <v>6.889027770196993E-50</v>
+        <v>3.854730706358897E-29</v>
       </c>
     </row>
     <row r="153">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B153">
-        <v>1.887020819268782</v>
+        <v>5.989181093940396</v>
       </c>
       <c r="C153">
-        <v>0.2384177602591086</v>
+        <v>3.373653873093454</v>
       </c>
       <c r="D153">
-        <v>7.91476615340232</v>
+        <v>1.775280250800788</v>
       </c>
       <c r="E153">
-        <v>4.193960455601617E-15</v>
+        <v>0.07601329231676832</v>
       </c>
     </row>
     <row r="154">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B154">
-        <v>1.595763626924553</v>
+        <v>4.376070296978064</v>
       </c>
       <c r="C154">
-        <v>0.2384177602591106</v>
+        <v>3.373653873093482</v>
       </c>
       <c r="D154">
-        <v>6.693140750883193</v>
+        <v>1.297130785075297</v>
       </c>
       <c r="E154">
-        <v>2.873480097560151E-11</v>
+        <v>0.1947452654502812</v>
       </c>
     </row>
     <row r="155">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B155">
-        <v>1.040889563726162</v>
+        <v>1.345374249779209</v>
       </c>
       <c r="C155">
-        <v>0.2392450476369336</v>
+        <v>3.385360137187738</v>
       </c>
       <c r="D155">
-        <v>4.350725643047642</v>
+        <v>0.3974094912385981</v>
       </c>
       <c r="E155">
-        <v>1.429612804399767E-05</v>
+        <v>0.6911106081351527</v>
       </c>
     </row>
     <row r="156">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B156">
-        <v>1.054535592848254</v>
+        <v>3.233823404163387</v>
       </c>
       <c r="C156">
-        <v>0.238417760259111</v>
+        <v>3.373653873093489</v>
       </c>
       <c r="D156">
-        <v>4.423058046104411</v>
+        <v>0.9585522183987761</v>
       </c>
       <c r="E156">
-        <v>1.028771976943869E-05</v>
+        <v>0.3379075607020722</v>
       </c>
     </row>
     <row r="157">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.6724595411250714</v>
+        <v>0.7943945235276234</v>
       </c>
       <c r="C157">
-        <v>0.2384177602591242</v>
+        <v>3.373653873093675</v>
       </c>
       <c r="D157">
-        <v>2.820509430145679</v>
+        <v>0.2354700729269407</v>
       </c>
       <c r="E157">
-        <v>0.004845042091138228</v>
+        <v>0.813869536851344</v>
       </c>
     </row>
     <row r="158">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B158">
-        <v>1.323900472816145</v>
+        <v>2.741308285607622</v>
       </c>
       <c r="C158">
-        <v>0.2384177602591093</v>
+        <v>3.373653873093464</v>
       </c>
       <c r="D158">
-        <v>5.552860119889338</v>
+        <v>0.8125635849815219</v>
       </c>
       <c r="E158">
-        <v>3.21017214013206E-08</v>
+        <v>0.4165711426159917</v>
       </c>
     </row>
     <row r="159">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B159">
-        <v>0.7690416371940327</v>
+        <v>1.653027072820572</v>
       </c>
       <c r="C159">
-        <v>0.239245047636949</v>
+        <v>3.385360137187956</v>
       </c>
       <c r="D159">
-        <v>3.214451646083987</v>
+        <v>0.4882869195103292</v>
       </c>
       <c r="E159">
-        <v>0.001329087462314722</v>
+        <v>0.6254035403647025</v>
       </c>
     </row>
     <row r="160">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B160">
-        <v>1.243278004275868</v>
+        <v>2.58049723415356</v>
       </c>
       <c r="C160">
-        <v>0.2383625056774885</v>
+        <v>3.372872010898767</v>
       </c>
       <c r="D160">
-        <v>5.21591263165382</v>
+        <v>0.7650741640403772</v>
       </c>
       <c r="E160">
-        <v>2.030656995457909E-07</v>
+        <v>0.4443233599834996</v>
       </c>
     </row>
     <row r="161">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B161">
-        <v>1.945317431257966</v>
+        <v>5.961076088649969</v>
       </c>
       <c r="C161">
-        <v>0.2384177602591079</v>
+        <v>3.373653873093445</v>
       </c>
       <c r="D161">
-        <v>8.159280706033947</v>
+        <v>1.766949519093377</v>
       </c>
       <c r="E161">
-        <v>6.096892064758013E-16</v>
+        <v>0.07739882190883489</v>
       </c>
     </row>
     <row r="162">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="B162">
-        <v>0.9517274842050244</v>
+        <v>1.58028779000677</v>
       </c>
       <c r="C162">
-        <v>0.2383625056774889</v>
+        <v>3.372872010898772</v>
       </c>
       <c r="D162">
-        <v>3.992773450253699</v>
+        <v>0.4685288338544661</v>
       </c>
       <c r="E162">
-        <v>6.781543930454271E-05</v>
+        <v>0.6394607454695945</v>
       </c>
     </row>
     <row r="163">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B163">
-        <v>1.269775663698514</v>
+        <v>2.571368582098348</v>
       </c>
       <c r="C163">
-        <v>0.2383625056774799</v>
+        <v>3.372872010898644</v>
       </c>
       <c r="D163">
-        <v>5.327078015435044</v>
+        <v>0.762367671761506</v>
       </c>
       <c r="E163">
-        <v>1.117842732936287E-07</v>
+        <v>0.445936180330222</v>
       </c>
     </row>
     <row r="164">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.9036764198790868</v>
+        <v>1.595552279852489</v>
       </c>
       <c r="C164">
-        <v>0.238362505677481</v>
+        <v>3.37287201089866</v>
       </c>
       <c r="D164">
-        <v>3.791185267626847</v>
+        <v>0.4730544991617912</v>
       </c>
       <c r="E164">
-        <v>0.0001546568324176119</v>
+        <v>0.6362291858031551</v>
       </c>
     </row>
     <row r="165">
@@ -3485,16 +3485,16 @@
         </is>
       </c>
       <c r="B165">
-        <v>1.252984743309531</v>
+        <v>2.979087549706262</v>
       </c>
       <c r="C165">
-        <v>0.2383625056774965</v>
+        <v>3.372872010898879</v>
       </c>
       <c r="D165">
-        <v>5.256635223514619</v>
+        <v>0.8832495096403992</v>
       </c>
       <c r="E165">
-        <v>1.633961603464225E-07</v>
+        <v>0.3772143449554927</v>
       </c>
     </row>
     <row r="166">
@@ -3504,16 +3504,16 @@
         </is>
       </c>
       <c r="B166">
-        <v>1.305569026746823</v>
+        <v>3.495304171922315</v>
       </c>
       <c r="C166">
-        <v>0.2384177602591134</v>
+        <v>3.373653873093521</v>
       </c>
       <c r="D166">
-        <v>5.475972198245322</v>
+        <v>1.03605891517177</v>
       </c>
       <c r="E166">
-        <v>4.93571947088183E-08</v>
+        <v>0.3003078301044225</v>
       </c>
     </row>
     <row r="167">
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="B167">
-        <v>2.10034844324456</v>
+        <v>7.32754536123614</v>
       </c>
       <c r="C167">
-        <v>0.2384177602591123</v>
+        <v>3.373653873093507</v>
       </c>
       <c r="D167">
-        <v>8.809530132998074</v>
+        <v>2.171990855279137</v>
       </c>
       <c r="E167">
-        <v>2.794738677907893E-18</v>
+        <v>0.02998091302623749</v>
       </c>
     </row>
     <row r="168">
@@ -3542,16 +3542,16 @@
         </is>
       </c>
       <c r="B168">
-        <v>0.7794614498404657</v>
+        <v>2.582715600711814</v>
       </c>
       <c r="C168">
-        <v>0.2384177602591108</v>
+        <v>3.373653873093485</v>
       </c>
       <c r="D168">
-        <v>3.269309505270716</v>
+        <v>0.7655544101041947</v>
       </c>
       <c r="E168">
-        <v>0.001097559067787902</v>
+        <v>0.444037525966878</v>
       </c>
     </row>
     <row r="169">
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="B169">
-        <v>1.224878773483028</v>
+        <v>2.447432672412441</v>
       </c>
       <c r="C169">
-        <v>0.2384177602591181</v>
+        <v>3.373653873093588</v>
       </c>
       <c r="D169">
-        <v>5.137531583854327</v>
+        <v>0.7254545855850302</v>
       </c>
       <c r="E169">
-        <v>3.072166489220505E-07</v>
+        <v>0.4682634386034392</v>
       </c>
     </row>
     <row r="170">
@@ -3580,16 +3580,16 @@
         </is>
       </c>
       <c r="B170">
-        <v>1.645535096566296</v>
+        <v>4.150786521046899</v>
       </c>
       <c r="C170">
-        <v>0.2384177602591082</v>
+        <v>3.373653873093448</v>
       </c>
       <c r="D170">
-        <v>6.901898142059373</v>
+        <v>1.230353402330769</v>
       </c>
       <c r="E170">
-        <v>6.988973657033242E-12</v>
+        <v>0.2187186363205462</v>
       </c>
     </row>
     <row r="171">
@@ -3599,16 +3599,16 @@
         </is>
       </c>
       <c r="B171">
-        <v>0.2502610243729218</v>
+        <v>0.4861161983026644</v>
       </c>
       <c r="C171">
-        <v>0.2383625056774858</v>
+        <v>3.372872010898729</v>
       </c>
       <c r="D171">
-        <v>1.049917744662137</v>
+        <v>0.1441253023334066</v>
       </c>
       <c r="E171">
-        <v>0.2938908039106329</v>
+        <v>0.8854169639801434</v>
       </c>
     </row>
     <row r="172">
@@ -3618,16 +3618,16 @@
         </is>
       </c>
       <c r="B172">
-        <v>1.035598973241663</v>
+        <v>1.796918946369389</v>
       </c>
       <c r="C172">
-        <v>0.238417760259113</v>
+        <v>3.373653873093517</v>
       </c>
       <c r="D172">
-        <v>4.343631833954698</v>
+        <v>0.5326328704615094</v>
       </c>
       <c r="E172">
-        <v>1.476111812814009E-05</v>
+        <v>0.5943506566297259</v>
       </c>
     </row>
     <row r="173">
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="B173">
-        <v>0.6005354249135165</v>
+        <v>1.074043019212845</v>
       </c>
       <c r="C173">
-        <v>0.2384177602591188</v>
+        <v>3.373653873093598</v>
       </c>
       <c r="D173">
-        <v>2.518836785736258</v>
+        <v>0.3183619480880416</v>
       </c>
       <c r="E173">
-        <v>0.01185664957047817</v>
+        <v>0.750245741533089</v>
       </c>
     </row>
     <row r="174">
@@ -3656,16 +3656,16 @@
         </is>
       </c>
       <c r="B174">
-        <v>1.809617838391756</v>
+        <v>6.945652751306114</v>
       </c>
       <c r="C174">
-        <v>0.2392450476369387</v>
+        <v>3.38536013718781</v>
       </c>
       <c r="D174">
-        <v>7.563867491785676</v>
+        <v>2.051673225252723</v>
       </c>
       <c r="E174">
-        <v>6.082861498498434E-14</v>
+        <v>0.04033961905881833</v>
       </c>
     </row>
     <row r="175">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="B175">
-        <v>1.7466065338104</v>
+        <v>5.297595524432756</v>
       </c>
       <c r="C175">
-        <v>0.23841776025911</v>
+        <v>3.373653873093474</v>
       </c>
       <c r="D175">
-        <v>7.325823931540191</v>
+        <v>1.570284244831294</v>
       </c>
       <c r="E175">
-        <v>3.50556326310544E-13</v>
+        <v>0.1165171863307095</v>
       </c>
     </row>
     <row r="176">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="B176">
-        <v>0.9739299910200756</v>
+        <v>1.594743287202192</v>
       </c>
       <c r="C176">
-        <v>0.2384177602591163</v>
+        <v>3.373653873093564</v>
       </c>
       <c r="D176">
-        <v>4.084972486787866</v>
+        <v>0.4727050691005976</v>
       </c>
       <c r="E176">
-        <v>4.593242304500967E-05</v>
+        <v>0.6364784513370028</v>
       </c>
     </row>
     <row r="177">
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="B177">
-        <v>1.100385323903542</v>
+        <v>2.175301340347579</v>
       </c>
       <c r="C177">
-        <v>0.2384177602591155</v>
+        <v>3.373653873093551</v>
       </c>
       <c r="D177">
-        <v>4.615366416946578</v>
+        <v>0.6447909068848505</v>
       </c>
       <c r="E177">
-        <v>4.18919536188892E-06</v>
+        <v>0.5191413233678412</v>
       </c>
     </row>
     <row r="178">
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="B178">
-        <v>2.082380371846882</v>
+        <v>7.894639457520523</v>
       </c>
       <c r="C178">
-        <v>0.2384177602591102</v>
+        <v>3.373653873093476</v>
       </c>
       <c r="D178">
-        <v>8.734166320427518</v>
+        <v>2.340085780726973</v>
       </c>
       <c r="E178">
-        <v>5.316857392778186E-18</v>
+        <v>0.0193833764169768</v>
       </c>
     </row>
     <row r="179">
@@ -3751,16 +3751,16 @@
         </is>
       </c>
       <c r="B179">
-        <v>1.066808109979539</v>
+        <v>1.990903121416444</v>
       </c>
       <c r="C179">
-        <v>0.2383625056774887</v>
+        <v>3.372872010898768</v>
       </c>
       <c r="D179">
-        <v>4.475570127723701</v>
+        <v>0.5902693950387783</v>
       </c>
       <c r="E179">
-        <v>8.077078663830872E-06</v>
+        <v>0.555080958043036</v>
       </c>
     </row>
     <row r="180">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="B180">
-        <v>1.193615021532132</v>
+        <v>2.28258830827798</v>
       </c>
       <c r="C180">
-        <v>0.2384177602591126</v>
+        <v>3.37365387309351</v>
       </c>
       <c r="D180">
-        <v>5.006401453628751</v>
+        <v>0.6765923221948478</v>
       </c>
       <c r="E180">
-        <v>6.063583089370971E-07</v>
+        <v>0.4987478400334835</v>
       </c>
     </row>
     <row r="181">
@@ -3789,16 +3789,16 @@
         </is>
       </c>
       <c r="B181">
-        <v>0.7388573064447421</v>
+        <v>1.025546496091325</v>
       </c>
       <c r="C181">
-        <v>0.2384177602591159</v>
+        <v>3.373653873093558</v>
       </c>
       <c r="D181">
-        <v>3.099002799295409</v>
+        <v>0.3039868743709988</v>
       </c>
       <c r="E181">
-        <v>0.001970473273241877</v>
+        <v>0.7611715137957419</v>
       </c>
     </row>
     <row r="182">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.1949383641161236</v>
+        <v>0.3755750132751641</v>
       </c>
       <c r="C182">
-        <v>0.2384177602591164</v>
+        <v>3.373653873093564</v>
       </c>
       <c r="D182">
-        <v>0.8176335685070666</v>
+        <v>0.1113258880143416</v>
       </c>
       <c r="E182">
-        <v>0.4136700071983465</v>
+        <v>0.9113698045964722</v>
       </c>
     </row>
     <row r="183">
@@ -3827,16 +3827,16 @@
         </is>
       </c>
       <c r="B183">
-        <v>0.9131697690526475</v>
+        <v>1.354062996066536</v>
       </c>
       <c r="C183">
-        <v>0.2384177602591043</v>
+        <v>3.373653873093394</v>
       </c>
       <c r="D183">
-        <v>3.83012476948129</v>
+        <v>0.4013639356621251</v>
       </c>
       <c r="E183">
-        <v>0.0001322767017436142</v>
+        <v>0.6881977889101193</v>
       </c>
     </row>
     <row r="184">
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="B184">
-        <v>1.561555115517556</v>
+        <v>3.826955725518999</v>
       </c>
       <c r="C184">
-        <v>0.2384177602591143</v>
+        <v>3.373653873093534</v>
       </c>
       <c r="D184">
-        <v>6.549659361871557</v>
+        <v>1.134365251883354</v>
       </c>
       <c r="E184">
-        <v>7.420268365345755E-11</v>
+        <v>0.256785907831608</v>
       </c>
     </row>
     <row r="185">
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="B185">
-        <v>3.270042241246874</v>
+        <v>29.05092028852055</v>
       </c>
       <c r="C185">
-        <v>0.2383625056774877</v>
+        <v>3.372872010898755</v>
       </c>
       <c r="D185">
-        <v>13.71877775807303</v>
+        <v>8.613110783524656</v>
       </c>
       <c r="E185">
-        <v>6.799522052973268E-41</v>
+        <v>1.478427886791569E-17</v>
       </c>
     </row>
     <row r="186">
@@ -3884,16 +3884,16 @@
         </is>
       </c>
       <c r="B186">
-        <v>1.429584604378105</v>
+        <v>3.314005767112039</v>
       </c>
       <c r="C186">
-        <v>0.2383625056774865</v>
+        <v>3.372872010898738</v>
       </c>
       <c r="D186">
-        <v>5.99752297583407</v>
+        <v>0.9825471456976471</v>
       </c>
       <c r="E186">
-        <v>2.396625271384886E-09</v>
+        <v>0.3259567270551735</v>
       </c>
     </row>
     <row r="187">
@@ -3903,16 +3903,16 @@
         </is>
       </c>
       <c r="B187">
-        <v>1.279113062650888</v>
+        <v>2.641393055985066</v>
       </c>
       <c r="C187">
-        <v>0.2383625056774829</v>
+        <v>3.372872010898686</v>
       </c>
       <c r="D187">
-        <v>5.366251118292891</v>
+        <v>0.7831287542041298</v>
       </c>
       <c r="E187">
-        <v>9.033131052904005E-08</v>
+        <v>0.4336500932390894</v>
       </c>
     </row>
     <row r="188">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="B188">
-        <v>1.451826375134172</v>
+        <v>3.456981936983722</v>
       </c>
       <c r="C188">
-        <v>0.2383625056774808</v>
+        <v>3.372872010898657</v>
       </c>
       <c r="D188">
-        <v>6.09083366953099</v>
+        <v>1.024937182855822</v>
       </c>
       <c r="E188">
-        <v>1.358558229837345E-09</v>
+        <v>0.3055246167907035</v>
       </c>
     </row>
     <row r="189">
@@ -3941,16 +3941,16 @@
         </is>
       </c>
       <c r="B189">
-        <v>1.485162157442061</v>
+        <v>3.441506704446324</v>
       </c>
       <c r="C189">
-        <v>0.2384177602591163</v>
+        <v>3.373653873093563</v>
       </c>
       <c r="D189">
-        <v>6.229242971781813</v>
+        <v>1.020112564568025</v>
       </c>
       <c r="E189">
-        <v>5.76780088801126E-10</v>
+        <v>0.307806260794495</v>
       </c>
     </row>
     <row r="190">
@@ -3960,16 +3960,16 @@
         </is>
       </c>
       <c r="B190">
-        <v>1.847065496267906</v>
+        <v>5.70435862435113</v>
       </c>
       <c r="C190">
-        <v>0.2383625056774898</v>
+        <v>3.372872010898784</v>
       </c>
       <c r="D190">
-        <v>7.748976673231613</v>
+        <v>1.691246690037036</v>
       </c>
       <c r="E190">
-        <v>1.504341495317249E-14</v>
+        <v>0.09095535048575032</v>
       </c>
     </row>
     <row r="191">
@@ -3979,16 +3979,16 @@
         </is>
       </c>
       <c r="B191">
-        <v>2.13157921380212</v>
+        <v>7.664650722490561</v>
       </c>
       <c r="C191">
-        <v>0.2383625056774894</v>
+        <v>3.372872010898779</v>
       </c>
       <c r="D191">
-        <v>8.942594422489421</v>
+        <v>2.272440429913657</v>
       </c>
       <c r="E191">
-        <v>8.870123725799563E-19</v>
+        <v>0.02317233294033373</v>
       </c>
     </row>
     <row r="192">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="B192">
-        <v>1.692028439928679</v>
+        <v>4.36130212796133</v>
       </c>
       <c r="C192">
-        <v>0.2384177602591147</v>
+        <v>3.37365387309354</v>
       </c>
       <c r="D192">
-        <v>7.096906027846946</v>
+        <v>1.29275328531618</v>
       </c>
       <c r="E192">
-        <v>1.800257689067792E-12</v>
+        <v>0.1962551671286989</v>
       </c>
     </row>
     <row r="193">
@@ -4017,16 +4017,16 @@
         </is>
       </c>
       <c r="B193">
-        <v>0.7354402899159879</v>
+        <v>1.122709641758728</v>
       </c>
       <c r="C193">
-        <v>0.2383625056774811</v>
+        <v>3.372872010898661</v>
       </c>
       <c r="D193">
-        <v>3.085385798515992</v>
+        <v>0.3328645848792808</v>
       </c>
       <c r="E193">
-        <v>0.002062488846291752</v>
+        <v>0.7392735975538602</v>
       </c>
     </row>
     <row r="194">
@@ -4036,16 +4036,16 @@
         </is>
       </c>
       <c r="B194">
-        <v>2.557753972194837</v>
+        <v>21.37612753977056</v>
       </c>
       <c r="C194">
-        <v>0.2383625056774943</v>
+        <v>3.372872010898848</v>
       </c>
       <c r="D194">
-        <v>10.73052141705328</v>
+        <v>6.337663412871088</v>
       </c>
       <c r="E194">
-        <v>4.098886670898835E-26</v>
+        <v>2.91223717173332E-10</v>
       </c>
     </row>
     <row r="195">
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="B195">
-        <v>2.022070203269079</v>
+        <v>6.533110398850456</v>
       </c>
       <c r="C195">
-        <v>0.2384177602591145</v>
+        <v>3.373653873093538</v>
       </c>
       <c r="D195">
-        <v>8.481206270336047</v>
+        <v>1.936508795687387</v>
       </c>
       <c r="E195">
-        <v>4.44018799529459E-17</v>
+        <v>0.05295502980735689</v>
       </c>
     </row>
     <row r="196">
@@ -4074,16 +4074,16 @@
         </is>
       </c>
       <c r="B196">
-        <v>1.888576616897027</v>
+        <v>6.196320021369959</v>
       </c>
       <c r="C196">
-        <v>0.2383625056774888</v>
+        <v>3.37287201089877</v>
       </c>
       <c r="D196">
-        <v>7.923127890979318</v>
+        <v>1.837104995786313</v>
       </c>
       <c r="E196">
-        <v>3.929747062629309E-15</v>
+        <v>0.06635207483071184</v>
       </c>
     </row>
     <row r="197">
@@ -4093,16 +4093,16 @@
         </is>
       </c>
       <c r="B197">
-        <v>1.928836948376388</v>
+        <v>6.314289514942205</v>
       </c>
       <c r="C197">
-        <v>0.2383625056774847</v>
+        <v>3.372872010898712</v>
       </c>
       <c r="D197">
-        <v>8.092031684656781</v>
+        <v>1.87208097269595</v>
       </c>
       <c r="E197">
-        <v>1.04171432486472E-15</v>
+        <v>0.06135046046177101</v>
       </c>
     </row>
     <row r="198">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="B198">
-        <v>1.392660688032729</v>
+        <v>3.219346161414982</v>
       </c>
       <c r="C198">
-        <v>0.2383625056774829</v>
+        <v>3.372872010898687</v>
       </c>
       <c r="D198">
-        <v>5.842616413493624</v>
+        <v>0.9544821597180029</v>
       </c>
       <c r="E198">
-        <v>6.041886356269447E-09</v>
+        <v>0.3399622786954846</v>
       </c>
     </row>
     <row r="199">
@@ -4131,16 +4131,16 @@
         </is>
       </c>
       <c r="B199">
-        <v>1.830114007858332</v>
+        <v>5.604999238563925</v>
       </c>
       <c r="C199">
-        <v>0.2383625056774895</v>
+        <v>3.37287201089878</v>
       </c>
       <c r="D199">
-        <v>7.67786025179028</v>
+        <v>1.661788298059476</v>
       </c>
       <c r="E199">
-        <v>2.582447304321067E-14</v>
+        <v>0.09672185961290537</v>
       </c>
     </row>
     <row r="200">
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="B200">
-        <v>2.495726418867436</v>
+        <v>11.97761072340476</v>
       </c>
       <c r="C200">
-        <v>0.238362505677487</v>
+        <v>3.372872010898744</v>
       </c>
       <c r="D200">
-        <v>10.47029780029349</v>
+        <v>3.551160756975528</v>
       </c>
       <c r="E200">
-        <v>5.662330054407146E-25</v>
+        <v>0.0003929716339308877</v>
       </c>
     </row>
     <row r="201">
@@ -4169,16 +4169,16 @@
         </is>
       </c>
       <c r="B201">
-        <v>2.168088288468583</v>
+        <v>8.395258245840891</v>
       </c>
       <c r="C201">
-        <v>0.2383625056774853</v>
+        <v>3.372872010898722</v>
       </c>
       <c r="D201">
-        <v>9.095760603398334</v>
+        <v>2.489053310861898</v>
       </c>
       <c r="E201">
-        <v>2.322488633811745E-19</v>
+        <v>0.01289424091794114</v>
       </c>
     </row>
     <row r="202">
@@ -4188,16 +4188,16 @@
         </is>
       </c>
       <c r="B202">
-        <v>1.571016547020298</v>
+        <v>4.675246224823791</v>
       </c>
       <c r="C202">
-        <v>0.2383625056774844</v>
+        <v>3.372872010898708</v>
       </c>
       <c r="D202">
-        <v>6.590871087527318</v>
+        <v>1.386132118181995</v>
       </c>
       <c r="E202">
-        <v>5.661267229558715E-11</v>
+        <v>0.1658708527575762</v>
       </c>
     </row>
     <row r="203">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B203">
-        <v>1.086786304170111</v>
+        <v>1.930476226118207</v>
       </c>
       <c r="C203">
-        <v>0.2383625056774928</v>
+        <v>3.372872010898827</v>
       </c>
       <c r="D203">
-        <v>4.559384459737744</v>
+        <v>0.572353833729896</v>
       </c>
       <c r="E203">
-        <v>5.460795849962276E-06</v>
+        <v>0.5671506840157751</v>
       </c>
     </row>
     <row r="204">
@@ -4226,16 +4226,16 @@
         </is>
       </c>
       <c r="B204">
-        <v>1.891172293468729</v>
+        <v>8.451490643935697</v>
       </c>
       <c r="C204">
-        <v>0.2383625056774898</v>
+        <v>3.372872010898785</v>
       </c>
       <c r="D204">
-        <v>7.934017508724843</v>
+        <v>2.50572527407691</v>
       </c>
       <c r="E204">
-        <v>3.610114678793071E-15</v>
+        <v>0.01230393156667056</v>
       </c>
     </row>
     <row r="205">
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="B205">
-        <v>2.353319401485621</v>
+        <v>10.15173544605926</v>
       </c>
       <c r="C205">
-        <v>0.238362505677487</v>
+        <v>3.372872010898745</v>
       </c>
       <c r="D205">
-        <v>9.872858966626849</v>
+        <v>3.009819350765758</v>
       </c>
       <c r="E205">
-        <v>1.897464874293497E-22</v>
+        <v>0.002648783307012441</v>
       </c>
     </row>
     <row r="206">
@@ -4264,16 +4264,16 @@
         </is>
       </c>
       <c r="B206">
-        <v>0.517703520598142</v>
+        <v>0.8254226561200214</v>
       </c>
       <c r="C206">
-        <v>0.2383625056774873</v>
+        <v>3.372872010898749</v>
       </c>
       <c r="D206">
-        <v>2.171916758160835</v>
+        <v>0.2447239780972525</v>
       </c>
       <c r="E206">
-        <v>0.02998651131563868</v>
+        <v>0.8066968533953698</v>
       </c>
     </row>
     <row r="207">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="B207">
-        <v>1.283519511959692</v>
+        <v>2.67292030056428</v>
       </c>
       <c r="C207">
-        <v>0.2383625056774858</v>
+        <v>3.372872010898727</v>
       </c>
       <c r="D207">
-        <v>5.384737454037116</v>
+        <v>0.7924760536205643</v>
       </c>
       <c r="E207">
-        <v>8.164921135168313E-08</v>
+        <v>0.4281830837690636</v>
       </c>
     </row>
     <row r="208">
@@ -4302,16 +4302,16 @@
         </is>
       </c>
       <c r="B208">
-        <v>2.226015549038755</v>
+        <v>13.72947952158322</v>
       </c>
       <c r="C208">
-        <v>0.2383625056774867</v>
+        <v>3.372872010898741</v>
       </c>
       <c r="D208">
-        <v>9.338782300143446</v>
+        <v>4.070560482941315</v>
       </c>
       <c r="E208">
-        <v>2.657542408488684E-20</v>
+        <v>4.884217738113093E-05</v>
       </c>
     </row>
     <row r="209">
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="B209">
-        <v>1.880427699295382</v>
+        <v>5.733394782726958</v>
       </c>
       <c r="C209">
-        <v>0.2383625056774873</v>
+        <v>3.372872010898749</v>
       </c>
       <c r="D209">
-        <v>7.888940812862852</v>
+        <v>1.69985542416097</v>
       </c>
       <c r="E209">
-        <v>5.125475899666693E-15</v>
+        <v>0.08932344902908457</v>
       </c>
     </row>
     <row r="210">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="B210">
-        <v>2.2179429948306</v>
+        <v>8.446105796251299</v>
       </c>
       <c r="C210">
-        <v>0.238362505677491</v>
+        <v>3.372872010898801</v>
       </c>
       <c r="D210">
-        <v>9.304915588660235</v>
+        <v>2.50412875702348</v>
       </c>
       <c r="E210">
-        <v>3.605841565305818E-20</v>
+        <v>0.01235940378612554</v>
       </c>
     </row>
     <row r="211">
@@ -4359,16 +4359,16 @@
         </is>
       </c>
       <c r="B211">
-        <v>1.66281309758502</v>
+        <v>4.472117833985313</v>
       </c>
       <c r="C211">
-        <v>0.2383625056774897</v>
+        <v>3.372872010898782</v>
       </c>
       <c r="D211">
-        <v>6.97598430113353</v>
+        <v>1.32590795604889</v>
       </c>
       <c r="E211">
-        <v>4.191580345562283E-12</v>
+        <v>0.1850311749507288</v>
       </c>
     </row>
     <row r="212">
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="B212">
-        <v>2.522571839981578</v>
+        <v>11.844528559712</v>
       </c>
       <c r="C212">
-        <v>0.238362505677486</v>
+        <v>3.37287201089873</v>
       </c>
       <c r="D212">
-        <v>10.5829221454599</v>
+        <v>3.511704126761668</v>
       </c>
       <c r="E212">
-        <v>1.830008820858633E-25</v>
+        <v>0.0004557453649008182</v>
       </c>
     </row>
     <row r="213">
@@ -4397,16 +4397,16 @@
         </is>
       </c>
       <c r="B213">
-        <v>0.6345172618042589</v>
+        <v>0.7351278780547139</v>
       </c>
       <c r="C213">
-        <v>0.2384177602591147</v>
+        <v>3.373653873093541</v>
       </c>
       <c r="D213">
-        <v>2.661367429652302</v>
+        <v>0.2179025785418299</v>
       </c>
       <c r="E213">
-        <v>0.007848610326202781</v>
+        <v>0.8275286532546883</v>
       </c>
     </row>
     <row r="214">
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="B214">
-        <v>1.294332278613412</v>
+        <v>2.723432642820076</v>
       </c>
       <c r="C214">
-        <v>0.2383625056774892</v>
+        <v>3.372872010898775</v>
       </c>
       <c r="D214">
-        <v>5.430100153271077</v>
+        <v>0.8074521161846157</v>
       </c>
       <c r="E214">
-        <v>6.363257366649634E-08</v>
+        <v>0.4195081425568331</v>
       </c>
     </row>
     <row r="215">
@@ -4435,16 +4435,16 @@
         </is>
       </c>
       <c r="B215">
-        <v>1.526283716306582</v>
+        <v>3.822142011455839</v>
       </c>
       <c r="C215">
-        <v>0.238362505677487</v>
+        <v>3.372872010898744</v>
       </c>
       <c r="D215">
-        <v>6.403203859468146</v>
+        <v>1.133201022483323</v>
       </c>
       <c r="E215">
-        <v>1.916692269847787E-10</v>
+        <v>0.2572742597458474</v>
       </c>
     </row>
     <row r="216">
@@ -4454,16 +4454,16 @@
         </is>
       </c>
       <c r="B216">
-        <v>1.264862570344236</v>
+        <v>2.571876778203027</v>
       </c>
       <c r="C216">
-        <v>0.2383625056774871</v>
+        <v>3.372872010898746</v>
       </c>
       <c r="D216">
-        <v>5.306466160645415</v>
+        <v>0.7625183433858544</v>
       </c>
       <c r="E216">
-        <v>1.249759147737537E-07</v>
+        <v>0.4458463062781199</v>
       </c>
     </row>
     <row r="217">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="B217">
-        <v>1.428900765087869</v>
+        <v>3.24544396887907</v>
       </c>
       <c r="C217">
-        <v>0.2383625056774891</v>
+        <v>3.372872010898774</v>
       </c>
       <c r="D217">
-        <v>5.994654071228846</v>
+        <v>0.9622197220624011</v>
       </c>
       <c r="E217">
-        <v>2.438509934829993E-09</v>
+        <v>0.336062920516473</v>
       </c>
     </row>
     <row r="218">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="B218">
-        <v>0.7597341854245357</v>
+        <v>1.36873329113538</v>
       </c>
       <c r="C218">
-        <v>0.2383625056774876</v>
+        <v>3.372872010898753</v>
       </c>
       <c r="D218">
-        <v>3.187305752073614</v>
+        <v>0.4058064719659078</v>
       </c>
       <c r="E218">
-        <v>0.00145963155895035</v>
+        <v>0.684930958482137</v>
       </c>
     </row>
     <row r="219">
@@ -4511,16 +4511,16 @@
         </is>
       </c>
       <c r="B219">
-        <v>1.336693300944595</v>
+        <v>2.780011223436118</v>
       </c>
       <c r="C219">
-        <v>0.2383625056774887</v>
+        <v>3.372872010898768</v>
       </c>
       <c r="D219">
-        <v>5.607816955713578</v>
+        <v>0.8242267167129561</v>
       </c>
       <c r="E219">
-        <v>2.352556379475354E-08</v>
+        <v>0.4099152478278358</v>
       </c>
     </row>
     <row r="220">
@@ -4530,16 +4530,16 @@
         </is>
       </c>
       <c r="B220">
-        <v>0.6134533648261669</v>
+        <v>0.3634654101178736</v>
       </c>
       <c r="C220">
-        <v>0.2392450476369388</v>
+        <v>3.38536013718781</v>
       </c>
       <c r="D220">
-        <v>2.564121476642225</v>
+        <v>0.1073638831287832</v>
       </c>
       <c r="E220">
-        <v>0.0104207823868008</v>
+        <v>0.9145117556543702</v>
       </c>
     </row>
     <row r="221">
@@ -4549,16 +4549,16 @@
         </is>
       </c>
       <c r="B221">
-        <v>2.924221923814241</v>
+        <v>19.0551963380826</v>
       </c>
       <c r="C221">
-        <v>0.2383625056774858</v>
+        <v>3.372872010898729</v>
       </c>
       <c r="D221">
-        <v>12.26796100126096</v>
+        <v>5.649546225445178</v>
       </c>
       <c r="E221">
-        <v>2.439766541433712E-33</v>
+        <v>1.854525307172895E-08</v>
       </c>
     </row>
     <row r="222">
@@ -4568,16 +4568,16 @@
         </is>
       </c>
       <c r="B222">
-        <v>-0.002907832263735539</v>
+        <v>0.08372660013514316</v>
       </c>
       <c r="C222">
-        <v>0.2383625056774869</v>
+        <v>3.372872010898743</v>
       </c>
       <c r="D222">
-        <v>-0.0121992016129833</v>
+        <v>0.02482353313870133</v>
       </c>
       <c r="E222">
-        <v>0.9902679804766898</v>
+        <v>0.9801983531638327</v>
       </c>
     </row>
     <row r="223">
@@ -4587,16 +4587,16 @@
         </is>
       </c>
       <c r="B223">
-        <v>1.983117679348973</v>
+        <v>7.76463492564623</v>
       </c>
       <c r="C223">
-        <v>0.2549315034530122</v>
+        <v>3.607326287534546</v>
       </c>
       <c r="D223">
-        <v>7.779021629292247</v>
+        <v>2.152462601588787</v>
       </c>
       <c r="E223">
-        <v>1.195660529339347E-14</v>
+        <v>0.03148779578940782</v>
       </c>
     </row>
     <row r="224">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="B224">
-        <v>1.11727285133146</v>
+        <v>2.347593677272408</v>
       </c>
       <c r="C224">
-        <v>0.2383625056774893</v>
+        <v>3.372872010898777</v>
       </c>
       <c r="D224">
-        <v>4.687284387097187</v>
+        <v>0.6960221644007297</v>
       </c>
       <c r="E224">
-        <v>2.967413226004878E-06</v>
+        <v>0.4865009375620527</v>
       </c>
     </row>
     <row r="225">
@@ -4625,16 +4625,16 @@
         </is>
       </c>
       <c r="B225">
-        <v>0.7836521095060728</v>
+        <v>1.060611607650367</v>
       </c>
       <c r="C225">
-        <v>0.2384177602591132</v>
+        <v>3.373653873093519</v>
       </c>
       <c r="D225">
-        <v>3.286886466236396</v>
+        <v>0.3143806826507144</v>
       </c>
       <c r="E225">
-        <v>0.001031666734297024</v>
+        <v>0.7532667907216236</v>
       </c>
     </row>
     <row r="226">
@@ -4644,16 +4644,16 @@
         </is>
       </c>
       <c r="B226">
-        <v>0.8356609264779919</v>
+        <v>1.3096563397499</v>
       </c>
       <c r="C226">
-        <v>0.238417760259113</v>
+        <v>3.373653873093516</v>
       </c>
       <c r="D226">
-        <v>3.505028004498464</v>
+        <v>0.3882011578588511</v>
       </c>
       <c r="E226">
-        <v>0.0004672512675742434</v>
+        <v>0.697911105605675</v>
       </c>
     </row>
     <row r="227">
@@ -4663,16 +4663,16 @@
         </is>
       </c>
       <c r="B227">
-        <v>0.3068441788608413</v>
+        <v>0.3411009308823758</v>
       </c>
       <c r="C227">
-        <v>0.2383625056774877</v>
+        <v>3.372872010898754</v>
       </c>
       <c r="D227">
-        <v>1.287300525679201</v>
+        <v>0.1011307069406064</v>
       </c>
       <c r="E227">
-        <v>0.1981479333910827</v>
+        <v>0.9194574805173841</v>
       </c>
     </row>
     <row r="228">
@@ -4682,16 +4682,16 @@
         </is>
       </c>
       <c r="B228">
-        <v>1.078176491078631</v>
+        <v>2.03426998772935</v>
       </c>
       <c r="C228">
-        <v>0.2384177602591132</v>
+        <v>3.373653873093518</v>
       </c>
       <c r="D228">
-        <v>4.522215500669351</v>
+        <v>0.6029871659193058</v>
       </c>
       <c r="E228">
-        <v>6.501214194690187E-06</v>
+        <v>0.5465899198914645</v>
       </c>
     </row>
     <row r="229">
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="B229">
-        <v>0.4483029767377209</v>
+        <v>0.5633397675886876</v>
       </c>
       <c r="C229">
-        <v>0.2383625056774875</v>
+        <v>3.372872010898752</v>
       </c>
       <c r="D229">
-        <v>1.880761302888341</v>
+        <v>0.1670207958583574</v>
       </c>
       <c r="E229">
-        <v>0.06015876668257972</v>
+        <v>0.8673716384911212</v>
       </c>
     </row>
     <row r="230">
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="B230">
-        <v>-0.2028308587596765</v>
+        <v>-0.2277414281034301</v>
       </c>
       <c r="C230">
-        <v>0.2383625056774874</v>
+        <v>3.37287201089875</v>
       </c>
       <c r="D230">
-        <v>-0.8509344126215619</v>
+        <v>-0.06752151500784198</v>
       </c>
       <c r="E230">
-        <v>0.3949140957802844</v>
+        <v>0.9461737107347723</v>
       </c>
     </row>
     <row r="231">
@@ -4739,16 +4739,16 @@
         </is>
       </c>
       <c r="B231">
-        <v>-0.688535635654568</v>
+        <v>-0.9642861948641751</v>
       </c>
       <c r="C231">
-        <v>0.2392450476369375</v>
+        <v>3.385360137187793</v>
       </c>
       <c r="D231">
-        <v>-2.87795146631183</v>
+        <v>-0.2848400630324679</v>
       </c>
       <c r="E231">
-        <v>0.004047844460898997</v>
+        <v>0.7757980333487341</v>
       </c>
     </row>
     <row r="232">
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="B232">
-        <v>-1.116468846957841</v>
+        <v>-1.256187474148723</v>
       </c>
       <c r="C232">
-        <v>0.2392450476369376</v>
+        <v>3.385360137187793</v>
       </c>
       <c r="D232">
-        <v>-4.666633052534989</v>
+        <v>-0.3710646499170495</v>
       </c>
       <c r="E232">
-        <v>3.277881152150085E-06</v>
+        <v>0.7106311659422102</v>
       </c>
     </row>
     <row r="233">
@@ -4777,16 +4777,16 @@
         </is>
       </c>
       <c r="B233">
-        <v>0.04409682509688193</v>
+        <v>-0.4682181769847862</v>
       </c>
       <c r="C233">
-        <v>0.2392450476369379</v>
+        <v>3.385360137187797</v>
       </c>
       <c r="D233">
-        <v>0.1843165638429444</v>
+        <v>-0.1383067555624179</v>
       </c>
       <c r="E233">
-        <v>0.8537849886450903</v>
+        <v>0.8900127907123158</v>
       </c>
     </row>
     <row r="234">
@@ -4796,16 +4796,16 @@
         </is>
       </c>
       <c r="B234">
-        <v>0.5966522220005953</v>
+        <v>1.040284069880966</v>
       </c>
       <c r="C234">
-        <v>0.2383625056774877</v>
+        <v>3.372872010898754</v>
       </c>
       <c r="D234">
-        <v>2.50312950983946</v>
+        <v>0.3084267848052041</v>
       </c>
       <c r="E234">
-        <v>0.01239423610540348</v>
+        <v>0.7577917557166987</v>
       </c>
     </row>
     <row r="235">
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="B235">
-        <v>0.6507631739455044</v>
+        <v>0.8942756466875589</v>
       </c>
       <c r="C235">
-        <v>0.2383625056774881</v>
+        <v>3.37287201089876</v>
       </c>
       <c r="D235">
-        <v>2.730140682553519</v>
+        <v>0.2651377353774132</v>
       </c>
       <c r="E235">
-        <v>0.006389764262644519</v>
+        <v>0.7909324103521131</v>
       </c>
     </row>
     <row r="236">
@@ -4834,16 +4834,16 @@
         </is>
       </c>
       <c r="B236">
-        <v>1.600621832787894</v>
+        <v>4.18640411990043</v>
       </c>
       <c r="C236">
-        <v>0.2384177602591138</v>
+        <v>3.373653873093527</v>
       </c>
       <c r="D236">
-        <v>6.713517613152345</v>
+        <v>1.240910975867729</v>
       </c>
       <c r="E236">
-        <v>2.507462441548297E-11</v>
+        <v>0.2147933779257829</v>
       </c>
     </row>
     <row r="237">
@@ -4853,16 +4853,16 @@
         </is>
       </c>
       <c r="B237">
-        <v>0.229223543301472</v>
+        <v>0.1199500207499617</v>
       </c>
       <c r="C237">
-        <v>0.2384177602591137</v>
+        <v>3.373653873093526</v>
       </c>
       <c r="D237">
-        <v>0.9614365265924425</v>
+        <v>0.03555492805786019</v>
       </c>
       <c r="E237">
-        <v>0.3364562978292747</v>
+        <v>0.9716410203388816</v>
       </c>
     </row>
     <row r="238">
@@ -4872,16 +4872,16 @@
         </is>
       </c>
       <c r="B238">
-        <v>0.6117488206179489</v>
+        <v>0.8354742736564824</v>
       </c>
       <c r="C238">
-        <v>0.2383625056774877</v>
+        <v>3.372872010898754</v>
       </c>
       <c r="D238">
-        <v>2.566464129411633</v>
+        <v>0.2477041141664481</v>
       </c>
       <c r="E238">
-        <v>0.01035090453340815</v>
+        <v>0.804390383785304</v>
       </c>
     </row>
     <row r="239">
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="B239">
-        <v>0.7915951670986062</v>
+        <v>1.053111275743174</v>
       </c>
       <c r="C239">
-        <v>0.2384177602591137</v>
+        <v>3.373653873093526</v>
       </c>
       <c r="D239">
-        <v>3.320202178890936</v>
+        <v>0.3121574753540162</v>
       </c>
       <c r="E239">
-        <v>0.0009167178394002086</v>
+        <v>0.7549554465949671</v>
       </c>
     </row>
     <row r="240">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="B240">
-        <v>0.02056373458346937</v>
+        <v>0.4999605076567253</v>
       </c>
       <c r="C240">
-        <v>0.04644992571815337</v>
+        <v>0.65727474175433</v>
       </c>
       <c r="D240">
-        <v>0.4427075881293117</v>
+        <v>0.7606568089354571</v>
       </c>
       <c r="E240">
-        <v>0.6580281561219907</v>
+        <v>0.4469574162956552</v>
       </c>
     </row>
     <row r="241">
@@ -4929,16 +4929,16 @@
         </is>
       </c>
       <c r="B241">
-        <v>-0.01576821858603338</v>
+        <v>0.4522624254802085</v>
       </c>
       <c r="C241">
-        <v>0.04650612725024664</v>
+        <v>0.6580700034672753</v>
       </c>
       <c r="D241">
-        <v>-0.3390567978534432</v>
+        <v>0.6872557981632705</v>
       </c>
       <c r="E241">
-        <v>0.7346047897503057</v>
+        <v>0.4920062717719801</v>
       </c>
     </row>
     <row r="242">
@@ -4948,16 +4948,16 @@
         </is>
       </c>
       <c r="B242">
-        <v>0.1214651955942655</v>
+        <v>1.661516756045842</v>
       </c>
       <c r="C242">
-        <v>0.04650612725024695</v>
+        <v>0.6580700034672796</v>
       </c>
       <c r="D242">
-        <v>2.611810588756786</v>
+        <v>2.524832840414455</v>
       </c>
       <c r="E242">
-        <v>0.00907805580431185</v>
+        <v>0.01165695460109997</v>
       </c>
     </row>
     <row r="243">
@@ -4967,16 +4967,16 @@
         </is>
       </c>
       <c r="B243">
-        <v>0.209001454680661</v>
+        <v>2.172143005444934</v>
       </c>
       <c r="C243">
-        <v>0.046507323687834</v>
+        <v>0.6580869332727399</v>
       </c>
       <c r="D243">
-        <v>4.493947148701106</v>
+        <v>3.300693108496507</v>
       </c>
       <c r="E243">
-        <v>7.41691435161001E-06</v>
+        <v>0.0009824988443072839</v>
       </c>
     </row>
     <row r="244">
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="B244">
-        <v>0.2320643559228965</v>
+        <v>2.567545790503777</v>
       </c>
       <c r="C244">
-        <v>0.05028884328367404</v>
+        <v>0.7115961106797412</v>
       </c>
       <c r="D244">
-        <v>4.614629026439245</v>
+        <v>3.608150398758038</v>
       </c>
       <c r="E244">
-        <v>4.203927849758151E-06</v>
+        <v>0.0003164447223596327</v>
       </c>
     </row>
     <row r="245">
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="B245">
-        <v>0.3048754669891903</v>
+        <v>3.245361557706682</v>
       </c>
       <c r="C245">
-        <v>0.05844649334828683</v>
+        <v>0.8270283155033773</v>
       </c>
       <c r="D245">
-        <v>5.216317515790307</v>
+        <v>3.924123874442397</v>
       </c>
       <c r="E245">
-        <v>2.026288767494425E-07</v>
+        <v>9.017665947831706E-05</v>
       </c>
     </row>
     <row r="246">
@@ -5024,16 +5024,16 @@
         </is>
       </c>
       <c r="B246">
-        <v>0.2668700177082472</v>
+        <v>3.25026121110615</v>
       </c>
       <c r="C246">
-        <v>0.05844649334828689</v>
+        <v>0.8270283155033783</v>
       </c>
       <c r="D246">
-        <v>4.566056959447497</v>
+        <v>3.930048282721553</v>
       </c>
       <c r="E246">
-        <v>5.291764371023938E-06</v>
+        <v>8.800109912295339E-05</v>
       </c>
     </row>
     <row r="247">
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="B247">
-        <v>0.35435641951097</v>
+        <v>3.541223426907625</v>
       </c>
       <c r="C247">
-        <v>0.05866007277327204</v>
+        <v>0.8300505024978838</v>
       </c>
       <c r="D247">
-        <v>6.040845207959398</v>
+        <v>4.266274661904266</v>
       </c>
       <c r="E247">
-        <v>1.843221209309652E-09</v>
+        <v>2.086356876924304E-05</v>
       </c>
     </row>
   </sheetData>
